--- a/outputs/generated/nitro_bioisostere_campaign/mol2mol_mmp/reinforcement_learning/mol2mol_mmp_rl_generated_optimal.xlsx
+++ b/outputs/generated/nitro_bioisostere_campaign/mol2mol_mmp/reinforcement_learning/mol2mol_mmp_rl_generated_optimal.xlsx
@@ -3190,7 +3190,7 @@
         <v>0.1430935290674003</v>
       </c>
       <c r="J2" s="3">
-        <v>1.390252001751471</v>
+        <v>1.390252001751472</v>
       </c>
       <c r="K2" s="3">
         <v>5.8569064709326</v>
@@ -3214,10 +3214,10 @@
         <v>0.6709746263398718</v>
       </c>
       <c r="R2" s="3">
-        <v>0.2177573738200021</v>
+        <v>0.217757373820002</v>
       </c>
       <c r="S2" s="3">
-        <v>92.93801779458317</v>
+        <v>92.93801779458316</v>
       </c>
       <c r="T2" s="3">
         <v>4.031806594500305</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="AA2" s="3">
-        <v>36.15313720703125</v>
+        <v>36.153137</v>
       </c>
       <c r="AB2" s="3">
-        <v>30.18597412109375</v>
+        <v>30.185974</v>
       </c>
       <c r="AC2" s="3">
-        <v>51.35652923583984</v>
+        <v>51.35653</v>
       </c>
       <c r="AD2" s="3">
         <v>0</v>
@@ -3261,55 +3261,55 @@
         <v>0</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.1472664028406143</v>
+        <v>0.1472664</v>
       </c>
       <c r="AH2" s="3">
-        <v>0.5605788826942444</v>
+        <v>0.5605789</v>
       </c>
       <c r="AI2" s="3">
-        <v>0.689824104309082</v>
+        <v>0.6898241000000001</v>
       </c>
       <c r="AJ2" s="3">
-        <v>0.1780272424221039</v>
+        <v>0.17802724</v>
       </c>
       <c r="AK2" s="3">
-        <v>0.9353399276733398</v>
+        <v>0.9353399</v>
       </c>
       <c r="AL2" s="3">
-        <v>0.1612811386585236</v>
+        <v>0.16128114</v>
       </c>
       <c r="AM2" s="3">
-        <v>0.4746731221675873</v>
+        <v>0.47467312</v>
       </c>
       <c r="AN2" s="3">
-        <v>0.6338269114494324</v>
+        <v>0.6338269</v>
       </c>
       <c r="AO2" s="3">
-        <v>0.4491912424564362</v>
+        <v>0.44919124</v>
       </c>
       <c r="AP2" s="3">
-        <v>0.939244270324707</v>
+        <v>0.9392443</v>
       </c>
       <c r="AQ2" s="3">
-        <v>0.9983583688735962</v>
+        <v>0.9983583700000001</v>
       </c>
       <c r="AR2" s="3">
-        <v>0.6840332746505737</v>
+        <v>0.6840333</v>
       </c>
       <c r="AS2" s="3">
-        <v>0.8427881002426147</v>
+        <v>0.8427881</v>
       </c>
       <c r="AT2" s="3">
-        <v>0.8624755144119263</v>
+        <v>0.8624755</v>
       </c>
       <c r="AU2" s="3">
-        <v>-5.189655303955078</v>
+        <v>-5.1896553</v>
       </c>
       <c r="AV2" s="3">
-        <v>96.65824127197266</v>
+        <v>96.65824000000001</v>
       </c>
       <c r="AW2" s="3">
-        <v>13.99696826934814</v>
+        <v>13.996968</v>
       </c>
       <c r="AX2" s="3">
         <v>464.6100000000003</v>
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="AA3" s="3">
-        <v>37.79553985595703</v>
+        <v>37.79554</v>
       </c>
       <c r="AB3" s="3">
-        <v>34.14446258544922</v>
+        <v>34.144463</v>
       </c>
       <c r="AC3" s="3">
-        <v>42.60309600830078</v>
+        <v>42.603096</v>
       </c>
       <c r="AD3" s="3">
         <v>0</v>
@@ -3442,55 +3442,55 @@
         <v>0</v>
       </c>
       <c r="AG3" s="3">
-        <v>0.1699026525020599</v>
+        <v>0.16990265</v>
       </c>
       <c r="AH3" s="3">
-        <v>0.3739382922649384</v>
+        <v>0.3739383</v>
       </c>
       <c r="AI3" s="3">
-        <v>0.8729871511459351</v>
+        <v>0.87298715</v>
       </c>
       <c r="AJ3" s="3">
-        <v>0.0723285973072052</v>
+        <v>0.07232860000000001</v>
       </c>
       <c r="AK3" s="3">
-        <v>0.8478779792785645</v>
+        <v>0.847878</v>
       </c>
       <c r="AL3" s="3">
-        <v>0.06567655503749847</v>
+        <v>0.065676555</v>
       </c>
       <c r="AM3" s="3">
-        <v>0.3315224647521973</v>
+        <v>0.33152246</v>
       </c>
       <c r="AN3" s="3">
-        <v>0.6256219744682312</v>
+        <v>0.625622</v>
       </c>
       <c r="AO3" s="3">
-        <v>0.09675826132297516</v>
+        <v>0.09675826</v>
       </c>
       <c r="AP3" s="3">
-        <v>0.9551485776901245</v>
+        <v>0.9551486</v>
       </c>
       <c r="AQ3" s="3">
-        <v>0.9994401931762695</v>
+        <v>0.9994402</v>
       </c>
       <c r="AR3" s="3">
-        <v>0.7929629683494568</v>
+        <v>0.79296297</v>
       </c>
       <c r="AS3" s="3">
-        <v>0.9054442644119263</v>
+        <v>0.90544426</v>
       </c>
       <c r="AT3" s="3">
-        <v>0.8638018369674683</v>
+        <v>0.86380184</v>
       </c>
       <c r="AU3" s="3">
-        <v>-5.089823722839355</v>
+        <v>-5.0898237</v>
       </c>
       <c r="AV3" s="3">
-        <v>97.52565765380859</v>
+        <v>97.52566</v>
       </c>
       <c r="AW3" s="3">
-        <v>6.958212375640869</v>
+        <v>6.9582124</v>
       </c>
       <c r="AX3" s="3">
         <v>459.5940000000003</v>
@@ -3499,7 +3499,7 @@
         <v>3.437100000000002</v>
       </c>
       <c r="AZ3" s="3">
-        <v>0.3748521174072291</v>
+        <v>0.374852117407229</v>
       </c>
       <c r="BA3" s="3">
         <v>4</v>
@@ -3605,13 +3605,13 @@
         </is>
       </c>
       <c r="AA4" s="3">
-        <v>41.49889373779297</v>
+        <v>41.498894</v>
       </c>
       <c r="AB4" s="3">
-        <v>26.97182655334473</v>
+        <v>26.971827</v>
       </c>
       <c r="AC4" s="3">
-        <v>42.35152816772461</v>
+        <v>42.35153</v>
       </c>
       <c r="AD4" s="3">
         <v>0</v>
@@ -3623,55 +3623,55 @@
         <v>0</v>
       </c>
       <c r="AG4" s="3">
-        <v>0.1439180821180344</v>
+        <v>0.14391808</v>
       </c>
       <c r="AH4" s="3">
-        <v>0.3220789432525635</v>
+        <v>0.32207894</v>
       </c>
       <c r="AI4" s="3">
-        <v>0.8559767603874207</v>
+        <v>0.85597676</v>
       </c>
       <c r="AJ4" s="3">
-        <v>0.1077740788459778</v>
+        <v>0.10777408</v>
       </c>
       <c r="AK4" s="3">
-        <v>0.7715238332748413</v>
+        <v>0.77152383</v>
       </c>
       <c r="AL4" s="3">
-        <v>0.141010969877243</v>
+        <v>0.14101097</v>
       </c>
       <c r="AM4" s="3">
-        <v>0.3957087993621826</v>
+        <v>0.3957088</v>
       </c>
       <c r="AN4" s="3">
-        <v>0.6398535966873169</v>
+        <v>0.6398536</v>
       </c>
       <c r="AO4" s="3">
-        <v>0.1372961699962616</v>
+        <v>0.13729617</v>
       </c>
       <c r="AP4" s="3">
-        <v>0.9219546318054199</v>
+        <v>0.92195463</v>
       </c>
       <c r="AQ4" s="3">
-        <v>0.9986831545829773</v>
+        <v>0.99868315</v>
       </c>
       <c r="AR4" s="3">
-        <v>0.7922579050064087</v>
+        <v>0.7922579</v>
       </c>
       <c r="AS4" s="3">
-        <v>0.8886443972587585</v>
+        <v>0.8886444</v>
       </c>
       <c r="AT4" s="3">
-        <v>0.7926870584487915</v>
+        <v>0.79268706</v>
       </c>
       <c r="AU4" s="3">
-        <v>-5.090410709381104</v>
+        <v>-5.0904107</v>
       </c>
       <c r="AV4" s="3">
-        <v>98.59910583496094</v>
+        <v>98.59910600000001</v>
       </c>
       <c r="AW4" s="3">
-        <v>7.195452690124512</v>
+        <v>7.1954527</v>
       </c>
       <c r="AX4" s="3">
         <v>433.5560000000002</v>
@@ -3757,7 +3757,7 @@
         <v>0.5951596058731246</v>
       </c>
       <c r="R5" s="3">
-        <v>0.4172456990781989</v>
+        <v>0.4172456990781988</v>
       </c>
       <c r="S5" s="3">
         <v>89.82919829885051</v>
@@ -3786,13 +3786,13 @@
         </is>
       </c>
       <c r="AA5" s="3">
-        <v>27.01364135742188</v>
+        <v>27.013641</v>
       </c>
       <c r="AB5" s="3">
-        <v>17.19558715820312</v>
+        <v>17.195587</v>
       </c>
       <c r="AC5" s="3">
-        <v>44.86339569091797</v>
+        <v>44.863396</v>
       </c>
       <c r="AD5" s="3">
         <v>0</v>
@@ -3804,55 +3804,55 @@
         <v>0</v>
       </c>
       <c r="AG5" s="3">
-        <v>0.1812024712562561</v>
+        <v>0.18120247</v>
       </c>
       <c r="AH5" s="3">
-        <v>0.5067104697227478</v>
+        <v>0.50671047</v>
       </c>
       <c r="AI5" s="3">
-        <v>0.5949105620384216</v>
+        <v>0.59491056</v>
       </c>
       <c r="AJ5" s="3">
-        <v>0.1587771028280258</v>
+        <v>0.1587771</v>
       </c>
       <c r="AK5" s="3">
-        <v>0.9621647000312805</v>
+        <v>0.9621647</v>
       </c>
       <c r="AL5" s="3">
-        <v>0.2237841635942459</v>
+        <v>0.22378416</v>
       </c>
       <c r="AM5" s="3">
-        <v>0.4548684060573578</v>
+        <v>0.4548684</v>
       </c>
       <c r="AN5" s="3">
-        <v>0.5593987107276917</v>
+        <v>0.5593987</v>
       </c>
       <c r="AO5" s="3">
-        <v>0.5417875051498413</v>
+        <v>0.5417875</v>
       </c>
       <c r="AP5" s="3">
-        <v>0.963330090045929</v>
+        <v>0.9633301</v>
       </c>
       <c r="AQ5" s="3">
-        <v>0.9989403486251831</v>
+        <v>0.99894035</v>
       </c>
       <c r="AR5" s="3">
-        <v>0.6388516426086426</v>
+        <v>0.6388516400000001</v>
       </c>
       <c r="AS5" s="3">
-        <v>0.872291088104248</v>
+        <v>0.8722911</v>
       </c>
       <c r="AT5" s="3">
-        <v>0.8383811712265015</v>
+        <v>0.8383812</v>
       </c>
       <c r="AU5" s="3">
-        <v>-5.346050262451172</v>
+        <v>-5.3460503</v>
       </c>
       <c r="AV5" s="3">
-        <v>92.82687377929688</v>
+        <v>92.82687</v>
       </c>
       <c r="AW5" s="3">
-        <v>14.08253479003906</v>
+        <v>14.082535</v>
       </c>
       <c r="AX5" s="3">
         <v>463.6260000000003</v>
@@ -3953,13 +3953,13 @@
         <v>0.5733752574286951</v>
       </c>
       <c r="W6" s="3">
-        <v>3.443700000000002</v>
+        <v>3.443700000000001</v>
       </c>
       <c r="X6" s="3">
         <v>-5.371076299549277</v>
       </c>
       <c r="Y6" s="3">
-        <v>4.255236479315838E-06</v>
+        <v>4.255236479315839E-06</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
@@ -3967,13 +3967,13 @@
         </is>
       </c>
       <c r="AA6" s="3">
-        <v>40.26303863525391</v>
+        <v>40.26304</v>
       </c>
       <c r="AB6" s="3">
-        <v>20.0941047668457</v>
+        <v>20.094105</v>
       </c>
       <c r="AC6" s="3">
-        <v>53.47330856323242</v>
+        <v>53.47331</v>
       </c>
       <c r="AD6" s="3">
         <v>0</v>
@@ -3985,61 +3985,61 @@
         <v>0</v>
       </c>
       <c r="AG6" s="3">
-        <v>0.104204036295414</v>
+        <v>0.10420404</v>
       </c>
       <c r="AH6" s="3">
-        <v>0.3238443732261658</v>
+        <v>0.32384437</v>
       </c>
       <c r="AI6" s="3">
-        <v>0.870003342628479</v>
+        <v>0.87000334</v>
       </c>
       <c r="AJ6" s="3">
-        <v>0.09911175072193146</v>
+        <v>0.09911175</v>
       </c>
       <c r="AK6" s="3">
-        <v>0.8365710973739624</v>
+        <v>0.8365711</v>
       </c>
       <c r="AL6" s="3">
-        <v>0.2092466652393341</v>
+        <v>0.20924667</v>
       </c>
       <c r="AM6" s="3">
-        <v>0.5164143443107605</v>
+        <v>0.51641434</v>
       </c>
       <c r="AN6" s="3">
-        <v>0.7787849903106689</v>
+        <v>0.7787849999999999</v>
       </c>
       <c r="AO6" s="3">
-        <v>0.1288960874080658</v>
+        <v>0.12889609</v>
       </c>
       <c r="AP6" s="3">
-        <v>0.9669011831283569</v>
+        <v>0.9669012</v>
       </c>
       <c r="AQ6" s="3">
-        <v>0.9994354248046875</v>
+        <v>0.9994354</v>
       </c>
       <c r="AR6" s="3">
-        <v>0.7853068113327026</v>
+        <v>0.7853068</v>
       </c>
       <c r="AS6" s="3">
-        <v>0.9309902191162109</v>
+        <v>0.9309902</v>
       </c>
       <c r="AT6" s="3">
-        <v>0.858154296875</v>
+        <v>0.8581543</v>
       </c>
       <c r="AU6" s="3">
-        <v>-5.143739223480225</v>
+        <v>-5.143739</v>
       </c>
       <c r="AV6" s="3">
-        <v>98.66546630859375</v>
+        <v>98.66547</v>
       </c>
       <c r="AW6" s="3">
-        <v>9.49403190612793</v>
+        <v>9.494032000000001</v>
       </c>
       <c r="AX6" s="3">
         <v>447.5830000000002</v>
       </c>
       <c r="AY6" s="3">
-        <v>3.443700000000002</v>
+        <v>3.443700000000001</v>
       </c>
       <c r="AZ6" s="3">
         <v>0.5032668594229877</v>
@@ -4140,7 +4140,7 @@
         <v>-4.697726188509208</v>
       </c>
       <c r="Y7" s="3">
-        <v>2.005736193847606E-05</v>
+        <v>2.005736193847605E-05</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="AA7" s="3">
-        <v>44.49736785888672</v>
+        <v>44.497368</v>
       </c>
       <c r="AB7" s="3">
-        <v>36.57278442382812</v>
+        <v>36.572784</v>
       </c>
       <c r="AC7" s="3">
-        <v>42.22423553466797</v>
+        <v>42.224236</v>
       </c>
       <c r="AD7" s="3">
         <v>0</v>
@@ -4166,55 +4166,55 @@
         <v>0</v>
       </c>
       <c r="AG7" s="3">
-        <v>0.121347464621067</v>
+        <v>0.121347465</v>
       </c>
       <c r="AH7" s="3">
-        <v>0.3793679475784302</v>
+        <v>0.37936795</v>
       </c>
       <c r="AI7" s="3">
-        <v>0.6308319568634033</v>
+        <v>0.63083196</v>
       </c>
       <c r="AJ7" s="3">
-        <v>0.06799261271953583</v>
+        <v>0.06799260999999999</v>
       </c>
       <c r="AK7" s="3">
-        <v>0.8862754702568054</v>
+        <v>0.8862755</v>
       </c>
       <c r="AL7" s="3">
-        <v>0.1875756233930588</v>
+        <v>0.18757562</v>
       </c>
       <c r="AM7" s="3">
-        <v>0.4857033789157867</v>
+        <v>0.48570338</v>
       </c>
       <c r="AN7" s="3">
-        <v>0.5998517274856567</v>
+        <v>0.5998517</v>
       </c>
       <c r="AO7" s="3">
-        <v>0.1621912717819214</v>
+        <v>0.16219127</v>
       </c>
       <c r="AP7" s="3">
-        <v>0.9689401388168335</v>
+        <v>0.9689401399999999</v>
       </c>
       <c r="AQ7" s="3">
-        <v>0.9997833967208862</v>
+        <v>0.9997834</v>
       </c>
       <c r="AR7" s="3">
-        <v>0.7327489852905273</v>
+        <v>0.732749</v>
       </c>
       <c r="AS7" s="3">
-        <v>0.9529389142990112</v>
+        <v>0.9529389</v>
       </c>
       <c r="AT7" s="3">
-        <v>0.8042116165161133</v>
+        <v>0.8042116</v>
       </c>
       <c r="AU7" s="3">
-        <v>-4.799037933349609</v>
+        <v>-4.799038</v>
       </c>
       <c r="AV7" s="3">
-        <v>94.31733703613281</v>
+        <v>94.31734</v>
       </c>
       <c r="AW7" s="3">
-        <v>12.3792028427124</v>
+        <v>12.379203</v>
       </c>
       <c r="AX7" s="3">
         <v>382.5520000000002</v>
@@ -4285,7 +4285,7 @@
         <v>1.146291335207776</v>
       </c>
       <c r="M8" s="3">
-        <v>0.3156389848610494</v>
+        <v>0.3156389848610493</v>
       </c>
       <c r="N8" s="3">
         <v>17.89272780624439</v>
@@ -4297,7 +4297,7 @@
         <v>4.853708664792224</v>
       </c>
       <c r="Q8" s="3">
-        <v>0.3156389848610494</v>
+        <v>0.3156389848610493</v>
       </c>
       <c r="R8" s="3">
         <v>3.370070024434588</v>
@@ -4312,7 +4312,7 @@
         <v>5.472361075119881</v>
       </c>
       <c r="V8" s="3">
-        <v>0.3156389848610494</v>
+        <v>0.3156389848610493</v>
       </c>
       <c r="W8" s="3">
         <v>3.489500000000002</v>
@@ -4321,7 +4321,7 @@
         <v>-5.14467691804052</v>
       </c>
       <c r="Y8" s="3">
-        <v>7.166763644850975E-06</v>
+        <v>7.166763644850976E-06</v>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
@@ -4329,13 +4329,13 @@
         </is>
       </c>
       <c r="AA8" s="3">
-        <v>60.57781982421875</v>
+        <v>60.57782</v>
       </c>
       <c r="AB8" s="3">
-        <v>51.04706573486328</v>
+        <v>51.047066</v>
       </c>
       <c r="AC8" s="3">
-        <v>46.69663619995117</v>
+        <v>46.696636</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -4347,55 +4347,55 @@
         <v>0</v>
       </c>
       <c r="AG8" s="3">
-        <v>0.08343183249235153</v>
+        <v>0.08343183</v>
       </c>
       <c r="AH8" s="3">
-        <v>0.2892420887947083</v>
+        <v>0.2892421</v>
       </c>
       <c r="AI8" s="3">
-        <v>0.828459620475769</v>
+        <v>0.8284596</v>
       </c>
       <c r="AJ8" s="3">
-        <v>0.07322672754526138</v>
+        <v>0.07322673</v>
       </c>
       <c r="AK8" s="3">
-        <v>0.8310872316360474</v>
+        <v>0.83108723</v>
       </c>
       <c r="AL8" s="3">
-        <v>0.3018696308135986</v>
+        <v>0.30186963</v>
       </c>
       <c r="AM8" s="3">
-        <v>0.5599618554115295</v>
+        <v>0.55996186</v>
       </c>
       <c r="AN8" s="3">
-        <v>0.7030657529830933</v>
+        <v>0.70306575</v>
       </c>
       <c r="AO8" s="3">
-        <v>0.09064048528671265</v>
+        <v>0.09064048500000001</v>
       </c>
       <c r="AP8" s="3">
-        <v>0.9627477526664734</v>
+        <v>0.96274775</v>
       </c>
       <c r="AQ8" s="3">
-        <v>0.999944806098938</v>
+        <v>0.9999448</v>
       </c>
       <c r="AR8" s="3">
-        <v>0.8073404431343079</v>
+        <v>0.80734044</v>
       </c>
       <c r="AS8" s="3">
-        <v>0.9643643498420715</v>
+        <v>0.96436435</v>
       </c>
       <c r="AT8" s="3">
-        <v>0.7601016163825989</v>
+        <v>0.7601016</v>
       </c>
       <c r="AU8" s="3">
-        <v>-4.802272796630859</v>
+        <v>-4.802273</v>
       </c>
       <c r="AV8" s="3">
-        <v>99.00502014160156</v>
+        <v>99.00502</v>
       </c>
       <c r="AW8" s="3">
-        <v>10.15865135192871</v>
+        <v>10.158651</v>
       </c>
       <c r="AX8" s="3">
         <v>405.5460000000002</v>
@@ -4510,13 +4510,13 @@
         </is>
       </c>
       <c r="AA9" s="3">
-        <v>64.52751159667969</v>
+        <v>64.52751000000001</v>
       </c>
       <c r="AB9" s="3">
-        <v>49.2342414855957</v>
+        <v>49.23424</v>
       </c>
       <c r="AC9" s="3">
-        <v>42.04615020751953</v>
+        <v>42.04615</v>
       </c>
       <c r="AD9" s="3">
         <v>0</v>
@@ -4528,55 +4528,55 @@
         <v>0</v>
       </c>
       <c r="AG9" s="3">
-        <v>0.1827121526002884</v>
+        <v>0.18271215</v>
       </c>
       <c r="AH9" s="3">
-        <v>0.4414897561073303</v>
+        <v>0.44148976</v>
       </c>
       <c r="AI9" s="3">
-        <v>0.5754063129425049</v>
+        <v>0.5754063</v>
       </c>
       <c r="AJ9" s="3">
-        <v>0.07122080773115158</v>
+        <v>0.07122081</v>
       </c>
       <c r="AK9" s="3">
-        <v>0.915116012096405</v>
+        <v>0.915116</v>
       </c>
       <c r="AL9" s="3">
-        <v>0.07872845232486725</v>
+        <v>0.07872845000000001</v>
       </c>
       <c r="AM9" s="3">
-        <v>0.5084763169288635</v>
+        <v>0.5084763</v>
       </c>
       <c r="AN9" s="3">
-        <v>0.558998703956604</v>
+        <v>0.5589987</v>
       </c>
       <c r="AO9" s="3">
-        <v>0.2247934341430664</v>
+        <v>0.22479343</v>
       </c>
       <c r="AP9" s="3">
-        <v>0.9602473378181458</v>
+        <v>0.96024734</v>
       </c>
       <c r="AQ9" s="3">
-        <v>0.9998801350593567</v>
+        <v>0.99988014</v>
       </c>
       <c r="AR9" s="3">
-        <v>0.6342812180519104</v>
+        <v>0.6342812</v>
       </c>
       <c r="AS9" s="3">
-        <v>0.9535814523696899</v>
+        <v>0.9535814500000001</v>
       </c>
       <c r="AT9" s="3">
-        <v>0.8581560850143433</v>
+        <v>0.8581561</v>
       </c>
       <c r="AU9" s="3">
-        <v>-4.801638603210449</v>
+        <v>-4.8016386</v>
       </c>
       <c r="AV9" s="3">
-        <v>97.19205474853516</v>
+        <v>97.192055</v>
       </c>
       <c r="AW9" s="3">
-        <v>12.07950115203857</v>
+        <v>12.079501</v>
       </c>
       <c r="AX9" s="3">
         <v>480.6530000000004</v>
@@ -4691,13 +4691,13 @@
         </is>
       </c>
       <c r="AA10" s="3">
-        <v>34.44804000854492</v>
+        <v>34.44804</v>
       </c>
       <c r="AB10" s="3">
-        <v>32.9227180480957</v>
+        <v>32.922718</v>
       </c>
       <c r="AC10" s="3">
-        <v>44.38904571533203</v>
+        <v>44.389046</v>
       </c>
       <c r="AD10" s="3">
         <v>0</v>
@@ -4709,55 +4709,55 @@
         <v>0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.1889603137969971</v>
+        <v>0.18896031</v>
       </c>
       <c r="AH10" s="3">
-        <v>0.237892746925354</v>
+        <v>0.23789275</v>
       </c>
       <c r="AI10" s="3">
-        <v>0.1465997844934464</v>
+        <v>0.14659978</v>
       </c>
       <c r="AJ10" s="3">
-        <v>0.07425312697887421</v>
+        <v>0.07425313</v>
       </c>
       <c r="AK10" s="3">
-        <v>0.9734166860580444</v>
+        <v>0.9734167</v>
       </c>
       <c r="AL10" s="3">
-        <v>0.05828919261693954</v>
+        <v>0.058289193</v>
       </c>
       <c r="AM10" s="3">
-        <v>0.1516631692647934</v>
+        <v>0.15166317</v>
       </c>
       <c r="AN10" s="3">
-        <v>0.1337379962205887</v>
+        <v>0.133738</v>
       </c>
       <c r="AO10" s="3">
-        <v>0.5682462453842163</v>
+        <v>0.56824625</v>
       </c>
       <c r="AP10" s="3">
-        <v>0.9111207723617554</v>
+        <v>0.9111208</v>
       </c>
       <c r="AQ10" s="3">
-        <v>0.9623255729675293</v>
+        <v>0.9623256</v>
       </c>
       <c r="AR10" s="3">
-        <v>0.3302415013313293</v>
+        <v>0.3302415</v>
       </c>
       <c r="AS10" s="3">
-        <v>0.7865296006202698</v>
+        <v>0.7865296000000001</v>
       </c>
       <c r="AT10" s="3">
-        <v>0.7827951908111572</v>
+        <v>0.7827952</v>
       </c>
       <c r="AU10" s="3">
-        <v>-5.124663352966309</v>
+        <v>-5.1246634</v>
       </c>
       <c r="AV10" s="3">
-        <v>89.681640625</v>
+        <v>89.68164</v>
       </c>
       <c r="AW10" s="3">
-        <v>16.0740852355957</v>
+        <v>16.074085</v>
       </c>
       <c r="AX10" s="3">
         <v>409.6220000000003</v>
@@ -4843,7 +4843,7 @@
         <v>0.2523153740755062</v>
       </c>
       <c r="R11" s="3">
-        <v>3.934977693460538</v>
+        <v>3.934977693460537</v>
       </c>
       <c r="S11" s="3">
         <v>38.37236272981531</v>
@@ -4872,13 +4872,13 @@
         </is>
       </c>
       <c r="AA11" s="3">
-        <v>49.28479766845703</v>
+        <v>49.284798</v>
       </c>
       <c r="AB11" s="3">
-        <v>43.93480682373047</v>
+        <v>43.934807</v>
       </c>
       <c r="AC11" s="3">
-        <v>55.54072189331055</v>
+        <v>55.54072</v>
       </c>
       <c r="AD11" s="3">
         <v>0</v>
@@ -4890,55 +4890,55 @@
         <v>0</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.2930010855197906</v>
+        <v>0.2930011</v>
       </c>
       <c r="AH11" s="3">
-        <v>0.5637204647064209</v>
+        <v>0.56372046</v>
       </c>
       <c r="AI11" s="3">
-        <v>0.567574143409729</v>
+        <v>0.5675741399999999</v>
       </c>
       <c r="AJ11" s="3">
-        <v>0.07100473344326019</v>
+        <v>0.07100473</v>
       </c>
       <c r="AK11" s="3">
-        <v>0.9091897010803223</v>
+        <v>0.9091897</v>
       </c>
       <c r="AL11" s="3">
-        <v>0.0736081451177597</v>
+        <v>0.073608145</v>
       </c>
       <c r="AM11" s="3">
-        <v>0.2517423331737518</v>
+        <v>0.25174233</v>
       </c>
       <c r="AN11" s="3">
-        <v>0.304872989654541</v>
+        <v>0.304873</v>
       </c>
       <c r="AO11" s="3">
-        <v>0.227603867650032</v>
+        <v>0.22760387</v>
       </c>
       <c r="AP11" s="3">
-        <v>0.8889592289924622</v>
+        <v>0.8889591999999999</v>
       </c>
       <c r="AQ11" s="3">
-        <v>0.9991973638534546</v>
+        <v>0.99919736</v>
       </c>
       <c r="AR11" s="3">
-        <v>0.7263250946998596</v>
+        <v>0.7263250999999999</v>
       </c>
       <c r="AS11" s="3">
-        <v>0.930528461933136</v>
+        <v>0.93052846</v>
       </c>
       <c r="AT11" s="3">
-        <v>0.8147878646850586</v>
+        <v>0.81478786</v>
       </c>
       <c r="AU11" s="3">
-        <v>-4.763751029968262</v>
+        <v>-4.763751</v>
       </c>
       <c r="AV11" s="3">
-        <v>94.78115844726562</v>
+        <v>94.78116</v>
       </c>
       <c r="AW11" s="3">
-        <v>14.94508934020996</v>
+        <v>14.945089</v>
       </c>
       <c r="AX11" s="3">
         <v>408.5900000000003</v>
@@ -5009,7 +5009,7 @@
         <v>1.226968975439208</v>
       </c>
       <c r="M12" s="3">
-        <v>0.3194719990151608</v>
+        <v>0.3194719990151607</v>
       </c>
       <c r="N12" s="3">
         <v>20.98277099426474</v>
@@ -5021,7 +5021,7 @@
         <v>4.773031024560792</v>
       </c>
       <c r="Q12" s="3">
-        <v>0.3194719990151608</v>
+        <v>0.3194719990151607</v>
       </c>
       <c r="R12" s="3">
         <v>3.988447294008948</v>
@@ -5036,7 +5036,7 @@
         <v>5.399196142630507</v>
       </c>
       <c r="V12" s="3">
-        <v>0.3194719990151608</v>
+        <v>0.3194719990151607</v>
       </c>
       <c r="W12" s="3">
         <v>2.2688</v>
@@ -5045,7 +5045,7 @@
         <v>-3.945832245423554</v>
       </c>
       <c r="Y12" s="3">
-        <v>0.0001132837859093375</v>
+        <v>0.0001132837859093</v>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
@@ -5053,13 +5053,13 @@
         </is>
       </c>
       <c r="AA12" s="3">
-        <v>25.22082901000977</v>
+        <v>25.220829</v>
       </c>
       <c r="AB12" s="3">
-        <v>35.52054595947266</v>
+        <v>35.520546</v>
       </c>
       <c r="AC12" s="3">
-        <v>41.39876174926758</v>
+        <v>41.39876</v>
       </c>
       <c r="AD12" s="3">
         <v>0</v>
@@ -5071,55 +5071,55 @@
         <v>0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.1336444318294525</v>
+        <v>0.13364443</v>
       </c>
       <c r="AH12" s="3">
-        <v>0.2904673218727112</v>
+        <v>0.29046732</v>
       </c>
       <c r="AI12" s="3">
-        <v>0.3785117268562317</v>
+        <v>0.37851173</v>
       </c>
       <c r="AJ12" s="3">
-        <v>0.1262486129999161</v>
+        <v>0.12624861</v>
       </c>
       <c r="AK12" s="3">
-        <v>0.9018864631652832</v>
+        <v>0.9018864599999999</v>
       </c>
       <c r="AL12" s="3">
-        <v>0.1279676407575607</v>
+        <v>0.12796764</v>
       </c>
       <c r="AM12" s="3">
-        <v>0.2456780225038528</v>
+        <v>0.24567802</v>
       </c>
       <c r="AN12" s="3">
-        <v>0.3470610082149506</v>
+        <v>0.347061</v>
       </c>
       <c r="AO12" s="3">
-        <v>0.3789393305778503</v>
+        <v>0.37893933</v>
       </c>
       <c r="AP12" s="3">
-        <v>0.8378087282180786</v>
+        <v>0.8378087</v>
       </c>
       <c r="AQ12" s="3">
-        <v>0.9808603525161743</v>
+        <v>0.98086035</v>
       </c>
       <c r="AR12" s="3">
-        <v>0.5761966705322266</v>
+        <v>0.5761967</v>
       </c>
       <c r="AS12" s="3">
-        <v>0.7470863461494446</v>
+        <v>0.74708635</v>
       </c>
       <c r="AT12" s="3">
-        <v>0.7338089942932129</v>
+        <v>0.733809</v>
       </c>
       <c r="AU12" s="3">
-        <v>-5.107641696929932</v>
+        <v>-5.1076417</v>
       </c>
       <c r="AV12" s="3">
-        <v>92.45306396484375</v>
+        <v>92.453064</v>
       </c>
       <c r="AW12" s="3">
-        <v>14.29115295410156</v>
+        <v>14.291153</v>
       </c>
       <c r="AX12" s="3">
         <v>371.5250000000001</v>
@@ -5220,7 +5220,7 @@
         <v>0.3201880795540402</v>
       </c>
       <c r="W13" s="3">
-        <v>3.304600000000002</v>
+        <v>3.304600000000001</v>
       </c>
       <c r="X13" s="3">
         <v>-5.098251673187821</v>
@@ -5234,13 +5234,13 @@
         </is>
       </c>
       <c r="AA13" s="3">
-        <v>39.24951934814453</v>
+        <v>39.24952</v>
       </c>
       <c r="AB13" s="3">
-        <v>40.82459259033203</v>
+        <v>40.824593</v>
       </c>
       <c r="AC13" s="3">
-        <v>47.84978485107422</v>
+        <v>47.849785</v>
       </c>
       <c r="AD13" s="3">
         <v>0</v>
@@ -5252,61 +5252,61 @@
         <v>0</v>
       </c>
       <c r="AG13" s="3">
-        <v>0.08766977488994598</v>
+        <v>0.08766977500000001</v>
       </c>
       <c r="AH13" s="3">
-        <v>0.4309412837028503</v>
+        <v>0.43094128</v>
       </c>
       <c r="AI13" s="3">
-        <v>0.6475259065628052</v>
+        <v>0.6475259</v>
       </c>
       <c r="AJ13" s="3">
-        <v>0.1673433780670166</v>
+        <v>0.16734338</v>
       </c>
       <c r="AK13" s="3">
-        <v>0.9045001864433289</v>
+        <v>0.9045002</v>
       </c>
       <c r="AL13" s="3">
-        <v>0.07176236808300018</v>
+        <v>0.07176237000000001</v>
       </c>
       <c r="AM13" s="3">
-        <v>0.3567617535591125</v>
+        <v>0.35676175</v>
       </c>
       <c r="AN13" s="3">
-        <v>0.5949729084968567</v>
+        <v>0.5949729</v>
       </c>
       <c r="AO13" s="3">
-        <v>0.2875572741031647</v>
+        <v>0.28755727</v>
       </c>
       <c r="AP13" s="3">
-        <v>0.9203920364379883</v>
+        <v>0.92039204</v>
       </c>
       <c r="AQ13" s="3">
-        <v>0.9973626136779785</v>
+        <v>0.9973626</v>
       </c>
       <c r="AR13" s="3">
-        <v>0.721953272819519</v>
+        <v>0.7219533</v>
       </c>
       <c r="AS13" s="3">
-        <v>0.8251237869262695</v>
+        <v>0.8251238</v>
       </c>
       <c r="AT13" s="3">
-        <v>0.7582597732543945</v>
+        <v>0.7582598</v>
       </c>
       <c r="AU13" s="3">
-        <v>-5.182535648345947</v>
+        <v>-5.1825356</v>
       </c>
       <c r="AV13" s="3">
-        <v>95.45188140869141</v>
+        <v>95.45188</v>
       </c>
       <c r="AW13" s="3">
-        <v>15.84775829315186</v>
+        <v>15.847758</v>
       </c>
       <c r="AX13" s="3">
         <v>421.5890000000002</v>
       </c>
       <c r="AY13" s="3">
-        <v>3.304600000000002</v>
+        <v>3.304600000000001</v>
       </c>
       <c r="AZ13" s="3">
         <v>0.4973094915903237</v>
@@ -5386,7 +5386,7 @@
         <v>0.3392971476612953</v>
       </c>
       <c r="R14" s="3">
-        <v>3.799627477626967</v>
+        <v>3.799627477626968</v>
       </c>
       <c r="S14" s="3">
         <v>81.24297878976041</v>
@@ -5415,13 +5415,13 @@
         </is>
       </c>
       <c r="AA14" s="3">
-        <v>45.19468307495117</v>
+        <v>45.194683</v>
       </c>
       <c r="AB14" s="3">
-        <v>41.36521530151367</v>
+        <v>41.365215</v>
       </c>
       <c r="AC14" s="3">
-        <v>47.65982055664062</v>
+        <v>47.65982</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -5433,55 +5433,55 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
-        <v>0.2197438776493073</v>
+        <v>0.21974388</v>
       </c>
       <c r="AH14" s="3">
-        <v>0.4637488424777985</v>
+        <v>0.46374884</v>
       </c>
       <c r="AI14" s="3">
-        <v>0.5675317049026489</v>
+        <v>0.5675317</v>
       </c>
       <c r="AJ14" s="3">
-        <v>0.1116752848029137</v>
+        <v>0.111675285</v>
       </c>
       <c r="AK14" s="3">
-        <v>0.9419897198677063</v>
+        <v>0.9419897</v>
       </c>
       <c r="AL14" s="3">
-        <v>0.08176111429929733</v>
+        <v>0.081761114</v>
       </c>
       <c r="AM14" s="3">
-        <v>0.3218612372875214</v>
+        <v>0.32186124</v>
       </c>
       <c r="AN14" s="3">
-        <v>0.3948546946048737</v>
+        <v>0.3948547</v>
       </c>
       <c r="AO14" s="3">
-        <v>0.3312728703022003</v>
+        <v>0.33127287</v>
       </c>
       <c r="AP14" s="3">
-        <v>0.9100964665412903</v>
+        <v>0.91009647</v>
       </c>
       <c r="AQ14" s="3">
-        <v>0.9989272952079773</v>
+        <v>0.9989273</v>
       </c>
       <c r="AR14" s="3">
-        <v>0.7198375463485718</v>
+        <v>0.71983755</v>
       </c>
       <c r="AS14" s="3">
-        <v>0.886700451374054</v>
+        <v>0.88670045</v>
       </c>
       <c r="AT14" s="3">
-        <v>0.7626605033874512</v>
+        <v>0.7626605</v>
       </c>
       <c r="AU14" s="3">
-        <v>-5.155337333679199</v>
+        <v>-5.1553373</v>
       </c>
       <c r="AV14" s="3">
-        <v>96.76426696777344</v>
+        <v>96.76427</v>
       </c>
       <c r="AW14" s="3">
-        <v>14.43843650817871</v>
+        <v>14.4384365</v>
       </c>
       <c r="AX14" s="3">
         <v>421.5890000000002</v>
@@ -5552,7 +5552,7 @@
         <v>0.8836030068125652</v>
       </c>
       <c r="M15" s="3">
-        <v>0.1803645338738968</v>
+        <v>0.1803645338738967</v>
       </c>
       <c r="N15" s="3">
         <v>8.32240433842561</v>
@@ -5564,7 +5564,7 @@
         <v>5.116396993187434</v>
       </c>
       <c r="Q15" s="3">
-        <v>0.1803645338738968</v>
+        <v>0.1803645338738967</v>
       </c>
       <c r="R15" s="3">
         <v>3.38913228359138</v>
@@ -5579,7 +5579,7 @@
         <v>5.469911479580272</v>
       </c>
       <c r="V15" s="3">
-        <v>0.1803645338738968</v>
+        <v>0.1803645338738967</v>
       </c>
       <c r="W15" s="3">
         <v>3.478700000000003</v>
@@ -5596,13 +5596,13 @@
         </is>
       </c>
       <c r="AA15" s="3">
-        <v>53.13448333740234</v>
+        <v>53.134483</v>
       </c>
       <c r="AB15" s="3">
-        <v>56.53021240234375</v>
+        <v>56.530212</v>
       </c>
       <c r="AC15" s="3">
-        <v>44.11493682861328</v>
+        <v>44.114937</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -5614,55 +5614,55 @@
         <v>0</v>
       </c>
       <c r="AG15" s="3">
-        <v>0.2469469308853149</v>
+        <v>0.24694693</v>
       </c>
       <c r="AH15" s="3">
-        <v>0.2810777723789215</v>
+        <v>0.28107777</v>
       </c>
       <c r="AI15" s="3">
-        <v>0.6463785171508789</v>
+        <v>0.6463785</v>
       </c>
       <c r="AJ15" s="3">
-        <v>0.05409278720617294</v>
+        <v>0.054092787</v>
       </c>
       <c r="AK15" s="3">
-        <v>0.8009153604507446</v>
+        <v>0.80091536</v>
       </c>
       <c r="AL15" s="3">
-        <v>0.206072524189949</v>
+        <v>0.20607252</v>
       </c>
       <c r="AM15" s="3">
-        <v>0.5045340061187744</v>
+        <v>0.504534</v>
       </c>
       <c r="AN15" s="3">
-        <v>0.5027914047241211</v>
+        <v>0.5027914</v>
       </c>
       <c r="AO15" s="3">
-        <v>0.09001478552818298</v>
+        <v>0.090014786</v>
       </c>
       <c r="AP15" s="3">
-        <v>0.9486678838729858</v>
+        <v>0.9486679</v>
       </c>
       <c r="AQ15" s="3">
-        <v>0.9999431371688843</v>
+        <v>0.99994314</v>
       </c>
       <c r="AR15" s="3">
-        <v>0.7472778558731079</v>
+        <v>0.74727786</v>
       </c>
       <c r="AS15" s="3">
-        <v>0.9748571515083313</v>
+        <v>0.97485715</v>
       </c>
       <c r="AT15" s="3">
-        <v>0.7642152309417725</v>
+        <v>0.76421523</v>
       </c>
       <c r="AU15" s="3">
-        <v>-4.632003784179688</v>
+        <v>-4.632004</v>
       </c>
       <c r="AV15" s="3">
-        <v>97.15895843505859</v>
+        <v>97.15895999999999</v>
       </c>
       <c r="AW15" s="3">
-        <v>10.61889266967773</v>
+        <v>10.618893</v>
       </c>
       <c r="AX15" s="3">
         <v>395.5470000000003</v>
@@ -5736,7 +5736,7 @@
         <v>0.2110704807218889</v>
       </c>
       <c r="N16" s="3">
-        <v>9.061066834644535</v>
+        <v>9.061066834644537</v>
       </c>
       <c r="O16" s="3">
         <v>4.568187854617745</v>
@@ -5751,7 +5751,7 @@
         <v>3.09826564858785</v>
       </c>
       <c r="S16" s="3">
-        <v>20.82164014079535</v>
+        <v>20.82164014079536</v>
       </c>
       <c r="T16" s="3">
         <v>4.681485063680344</v>
@@ -5777,13 +5777,13 @@
         </is>
       </c>
       <c r="AA16" s="3">
-        <v>61.72198486328125</v>
+        <v>61.721985</v>
       </c>
       <c r="AB16" s="3">
-        <v>65.67930603027344</v>
+        <v>65.679306</v>
       </c>
       <c r="AC16" s="3">
-        <v>43.52642059326172</v>
+        <v>43.52642</v>
       </c>
       <c r="AD16" s="3">
         <v>0</v>
@@ -5795,55 +5795,55 @@
         <v>0</v>
       </c>
       <c r="AG16" s="3">
-        <v>0.2642582952976227</v>
+        <v>0.2642583</v>
       </c>
       <c r="AH16" s="3">
-        <v>0.481314480304718</v>
+        <v>0.48131448</v>
       </c>
       <c r="AI16" s="3">
-        <v>0.5682402849197388</v>
+        <v>0.5682403</v>
       </c>
       <c r="AJ16" s="3">
-        <v>0.04729252308607101</v>
+        <v>0.047292523</v>
       </c>
       <c r="AK16" s="3">
-        <v>0.8873566389083862</v>
+        <v>0.88735664</v>
       </c>
       <c r="AL16" s="3">
-        <v>0.04412536695599556</v>
+        <v>0.044125367</v>
       </c>
       <c r="AM16" s="3">
-        <v>0.2427957355976105</v>
+        <v>0.24279574</v>
       </c>
       <c r="AN16" s="3">
-        <v>0.3247467577457428</v>
+        <v>0.32474676</v>
       </c>
       <c r="AO16" s="3">
-        <v>0.1160611286759377</v>
+        <v>0.11606113</v>
       </c>
       <c r="AP16" s="3">
-        <v>0.9488825798034668</v>
+        <v>0.9488826</v>
       </c>
       <c r="AQ16" s="3">
-        <v>0.999772846698761</v>
+        <v>0.99977285</v>
       </c>
       <c r="AR16" s="3">
-        <v>0.7162142395973206</v>
+        <v>0.71621424</v>
       </c>
       <c r="AS16" s="3">
-        <v>0.937679648399353</v>
+        <v>0.93767965</v>
       </c>
       <c r="AT16" s="3">
-        <v>0.7798179388046265</v>
+        <v>0.77981794</v>
       </c>
       <c r="AU16" s="3">
-        <v>-4.770207405090332</v>
+        <v>-4.7702074</v>
       </c>
       <c r="AV16" s="3">
-        <v>92.79644775390625</v>
+        <v>92.79644999999999</v>
       </c>
       <c r="AW16" s="3">
-        <v>14.58462810516357</v>
+        <v>14.584628</v>
       </c>
       <c r="AX16" s="3">
         <v>438.6160000000004</v>
@@ -5914,7 +5914,7 @@
         <v>0.9335827977048122</v>
       </c>
       <c r="M17" s="3">
-        <v>0.2311117008256361</v>
+        <v>0.231111700825636</v>
       </c>
       <c r="N17" s="3">
         <v>10.11017393761711</v>
@@ -5926,7 +5926,7 @@
         <v>5.066417202295188</v>
       </c>
       <c r="Q17" s="3">
-        <v>0.2311117008256361</v>
+        <v>0.231111700825636</v>
       </c>
       <c r="R17" s="3">
         <v>3.024153728232994</v>
@@ -5941,7 +5941,7 @@
         <v>5.519396135913435</v>
       </c>
       <c r="V17" s="3">
-        <v>0.2311117008256361</v>
+        <v>0.231111700825636</v>
       </c>
       <c r="W17" s="3">
         <v>3.126000000000002</v>
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="AA17" s="3">
-        <v>39.23947906494141</v>
+        <v>39.23948</v>
       </c>
       <c r="AB17" s="3">
-        <v>30.98924827575684</v>
+        <v>30.989248</v>
       </c>
       <c r="AC17" s="3">
-        <v>44.64337921142578</v>
+        <v>44.64338</v>
       </c>
       <c r="AD17" s="3">
         <v>0</v>
@@ -5976,55 +5976,55 @@
         <v>0</v>
       </c>
       <c r="AG17" s="3">
-        <v>0.3286693096160889</v>
+        <v>0.3286693</v>
       </c>
       <c r="AH17" s="3">
-        <v>0.3766919076442719</v>
+        <v>0.3766919</v>
       </c>
       <c r="AI17" s="3">
-        <v>0.2423591911792755</v>
+        <v>0.24235919</v>
       </c>
       <c r="AJ17" s="3">
-        <v>0.101474866271019</v>
+        <v>0.101474866</v>
       </c>
       <c r="AK17" s="3">
-        <v>0.9584389925003052</v>
+        <v>0.958439</v>
       </c>
       <c r="AL17" s="3">
-        <v>0.05315344408154488</v>
+        <v>0.053153444</v>
       </c>
       <c r="AM17" s="3">
-        <v>0.1350715458393097</v>
+        <v>0.13507155</v>
       </c>
       <c r="AN17" s="3">
-        <v>0.1181405782699585</v>
+        <v>0.11814058</v>
       </c>
       <c r="AO17" s="3">
-        <v>0.5811222791671753</v>
+        <v>0.5811223</v>
       </c>
       <c r="AP17" s="3">
-        <v>0.8536728024482727</v>
+        <v>0.8536728</v>
       </c>
       <c r="AQ17" s="3">
-        <v>0.9924591183662415</v>
+        <v>0.9924591</v>
       </c>
       <c r="AR17" s="3">
-        <v>0.4844502508640289</v>
+        <v>0.48445025</v>
       </c>
       <c r="AS17" s="3">
-        <v>0.8133481740951538</v>
+        <v>0.8133482</v>
       </c>
       <c r="AT17" s="3">
-        <v>0.7476910948753357</v>
+        <v>0.7476911000000001</v>
       </c>
       <c r="AU17" s="3">
-        <v>-5.110149383544922</v>
+        <v>-5.1101494</v>
       </c>
       <c r="AV17" s="3">
-        <v>90.67393493652344</v>
+        <v>90.673935</v>
       </c>
       <c r="AW17" s="3">
-        <v>14.40578174591064</v>
+        <v>14.405782</v>
       </c>
       <c r="AX17" s="3">
         <v>451.6590000000003</v>
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="AA18" s="3">
-        <v>54.334716796875</v>
+        <v>54.334717</v>
       </c>
       <c r="AB18" s="3">
-        <v>41.57420349121094</v>
+        <v>41.574203</v>
       </c>
       <c r="AC18" s="3">
-        <v>40.35257339477539</v>
+        <v>40.352573</v>
       </c>
       <c r="AD18" s="3">
         <v>0</v>
@@ -6157,55 +6157,55 @@
         <v>0</v>
       </c>
       <c r="AG18" s="3">
-        <v>0.3218770325183868</v>
+        <v>0.32187703</v>
       </c>
       <c r="AH18" s="3">
-        <v>0.3313052952289581</v>
+        <v>0.3313053</v>
       </c>
       <c r="AI18" s="3">
-        <v>0.8807485699653625</v>
+        <v>0.88074857</v>
       </c>
       <c r="AJ18" s="3">
-        <v>0.0869850367307663</v>
+        <v>0.08698504</v>
       </c>
       <c r="AK18" s="3">
-        <v>0.9104766845703125</v>
+        <v>0.9104767</v>
       </c>
       <c r="AL18" s="3">
-        <v>0.357574999332428</v>
+        <v>0.357575</v>
       </c>
       <c r="AM18" s="3">
-        <v>0.7273853421211243</v>
+        <v>0.72738534</v>
       </c>
       <c r="AN18" s="3">
-        <v>0.8768280148506165</v>
+        <v>0.8768280000000001</v>
       </c>
       <c r="AO18" s="3">
-        <v>0.1588038355112076</v>
+        <v>0.15880384</v>
       </c>
       <c r="AP18" s="3">
-        <v>0.9773505926132202</v>
+        <v>0.9773506</v>
       </c>
       <c r="AQ18" s="3">
-        <v>0.9999383091926575</v>
+        <v>0.9999382999999999</v>
       </c>
       <c r="AR18" s="3">
-        <v>0.6991746425628662</v>
+        <v>0.69917464</v>
       </c>
       <c r="AS18" s="3">
-        <v>0.9559606313705444</v>
+        <v>0.95596063</v>
       </c>
       <c r="AT18" s="3">
-        <v>0.9469095468521118</v>
+        <v>0.94690955</v>
       </c>
       <c r="AU18" s="3">
-        <v>-4.88031005859375</v>
+        <v>-4.88031</v>
       </c>
       <c r="AV18" s="3">
-        <v>104.4466171264648</v>
+        <v>104.44662</v>
       </c>
       <c r="AW18" s="3">
-        <v>3.686249256134033</v>
+        <v>3.6862493</v>
       </c>
       <c r="AX18" s="3">
         <v>469.5890000000002</v>
@@ -6214,7 +6214,7 @@
         <v>3.087100000000001</v>
       </c>
       <c r="AZ18" s="3">
-        <v>0.4816395979936337</v>
+        <v>0.4816395979936336</v>
       </c>
       <c r="BA18" s="3">
         <v>4</v>
@@ -6312,7 +6312,7 @@
         <v>-5.14467691804052</v>
       </c>
       <c r="Y19" s="3">
-        <v>7.166763644850975E-06</v>
+        <v>7.166763644850976E-06</v>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
@@ -6320,13 +6320,13 @@
         </is>
       </c>
       <c r="AA19" s="3">
-        <v>67.17526245117188</v>
+        <v>67.17525999999999</v>
       </c>
       <c r="AB19" s="3">
-        <v>61.51619720458984</v>
+        <v>61.516197</v>
       </c>
       <c r="AC19" s="3">
-        <v>45.63950347900391</v>
+        <v>45.639503</v>
       </c>
       <c r="AD19" s="3">
         <v>0</v>
@@ -6338,55 +6338,55 @@
         <v>0</v>
       </c>
       <c r="AG19" s="3">
-        <v>0.1720393598079681</v>
+        <v>0.17203936</v>
       </c>
       <c r="AH19" s="3">
-        <v>0.2651097178459167</v>
+        <v>0.26510972</v>
       </c>
       <c r="AI19" s="3">
-        <v>0.8181465864181519</v>
+        <v>0.8181465999999999</v>
       </c>
       <c r="AJ19" s="3">
-        <v>0.06401342898607254</v>
+        <v>0.06401343</v>
       </c>
       <c r="AK19" s="3">
-        <v>0.8541048169136047</v>
+        <v>0.8541048</v>
       </c>
       <c r="AL19" s="3">
-        <v>0.3996850550174713</v>
+        <v>0.39968506</v>
       </c>
       <c r="AM19" s="3">
-        <v>0.7441393733024597</v>
+        <v>0.7441394</v>
       </c>
       <c r="AN19" s="3">
-        <v>0.8027284741401672</v>
+        <v>0.8027285</v>
       </c>
       <c r="AO19" s="3">
-        <v>0.1312609910964966</v>
+        <v>0.13126099</v>
       </c>
       <c r="AP19" s="3">
-        <v>0.9818355441093445</v>
+        <v>0.98183554</v>
       </c>
       <c r="AQ19" s="3">
-        <v>0.9999833106994629</v>
+        <v>0.9999833</v>
       </c>
       <c r="AR19" s="3">
-        <v>0.7563844323158264</v>
+        <v>0.75638443</v>
       </c>
       <c r="AS19" s="3">
-        <v>0.9774829149246216</v>
+        <v>0.9774829</v>
       </c>
       <c r="AT19" s="3">
-        <v>0.8290756344795227</v>
+        <v>0.82907563</v>
       </c>
       <c r="AU19" s="3">
-        <v>-4.80022668838501</v>
+        <v>-4.8002267</v>
       </c>
       <c r="AV19" s="3">
-        <v>99.49089050292969</v>
+        <v>99.49088999999999</v>
       </c>
       <c r="AW19" s="3">
-        <v>9.877474784851074</v>
+        <v>9.877475</v>
       </c>
       <c r="AX19" s="3">
         <v>405.5460000000002</v>
@@ -6457,7 +6457,7 @@
         <v>1.177008860464088</v>
       </c>
       <c r="M20" s="3">
-        <v>0.2816135742041224</v>
+        <v>0.2816135742041223</v>
       </c>
       <c r="N20" s="3">
         <v>17.87159806152246</v>
@@ -6469,7 +6469,7 @@
         <v>4.822991139535912</v>
       </c>
       <c r="Q20" s="3">
-        <v>0.2816135742041224</v>
+        <v>0.2816135742041223</v>
       </c>
       <c r="R20" s="3">
         <v>4.217414190825265</v>
@@ -6484,7 +6484,7 @@
         <v>5.374953744975992</v>
       </c>
       <c r="V20" s="3">
-        <v>0.2816135742041224</v>
+        <v>0.2816135742041223</v>
       </c>
       <c r="W20" s="3">
         <v>3.202400000000002</v>
@@ -6501,13 +6501,13 @@
         </is>
       </c>
       <c r="AA20" s="3">
-        <v>47.49947357177734</v>
+        <v>47.499474</v>
       </c>
       <c r="AB20" s="3">
-        <v>29.84403038024902</v>
+        <v>29.84403</v>
       </c>
       <c r="AC20" s="3">
-        <v>48.45298767089844</v>
+        <v>48.452988</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
@@ -6519,55 +6519,55 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
-        <v>0.4535209536552429</v>
+        <v>0.45352095</v>
       </c>
       <c r="AH20" s="3">
-        <v>0.3859624266624451</v>
+        <v>0.38596243</v>
       </c>
       <c r="AI20" s="3">
-        <v>0.8907811045646667</v>
+        <v>0.8907811</v>
       </c>
       <c r="AJ20" s="3">
-        <v>0.0809163898229599</v>
+        <v>0.08091639</v>
       </c>
       <c r="AK20" s="3">
-        <v>0.9410744905471802</v>
+        <v>0.9410745</v>
       </c>
       <c r="AL20" s="3">
-        <v>0.4301293790340424</v>
+        <v>0.43012938</v>
       </c>
       <c r="AM20" s="3">
-        <v>0.8351858854293823</v>
+        <v>0.8351859</v>
       </c>
       <c r="AN20" s="3">
-        <v>0.9030261039733887</v>
+        <v>0.9030261000000001</v>
       </c>
       <c r="AO20" s="3">
-        <v>0.2547026574611664</v>
+        <v>0.25470266</v>
       </c>
       <c r="AP20" s="3">
-        <v>0.9865433573722839</v>
+        <v>0.98654336</v>
       </c>
       <c r="AQ20" s="3">
-        <v>0.999955952167511</v>
+        <v>0.99995595</v>
       </c>
       <c r="AR20" s="3">
-        <v>0.6654533743858337</v>
+        <v>0.6654534</v>
       </c>
       <c r="AS20" s="3">
-        <v>0.9484518766403198</v>
+        <v>0.9484519</v>
       </c>
       <c r="AT20" s="3">
-        <v>0.9595903158187866</v>
+        <v>0.9595903</v>
       </c>
       <c r="AU20" s="3">
-        <v>-5.089284420013428</v>
+        <v>-5.0892844</v>
       </c>
       <c r="AV20" s="3">
-        <v>101.8422775268555</v>
+        <v>101.84228</v>
       </c>
       <c r="AW20" s="3">
-        <v>6.237030029296875</v>
+        <v>6.23703</v>
       </c>
       <c r="AX20" s="3">
         <v>468.6050000000002</v>
@@ -6635,7 +6635,7 @@
         <v>5.302380392493043</v>
       </c>
       <c r="L21" s="3">
-        <v>1.131400390600839</v>
+        <v>1.131400390600838</v>
       </c>
       <c r="M21" s="3">
         <v>0.282597803225517</v>
@@ -6682,13 +6682,13 @@
         </is>
       </c>
       <c r="AA21" s="3">
-        <v>25.44314956665039</v>
+        <v>25.44315</v>
       </c>
       <c r="AB21" s="3">
-        <v>19.95843696594238</v>
+        <v>19.958437</v>
       </c>
       <c r="AC21" s="3">
-        <v>45.05075836181641</v>
+        <v>45.05076</v>
       </c>
       <c r="AD21" s="3">
         <v>0</v>
@@ -6700,55 +6700,55 @@
         <v>1</v>
       </c>
       <c r="AG21" s="3">
-        <v>0.1241066008806229</v>
+        <v>0.1241066</v>
       </c>
       <c r="AH21" s="3">
-        <v>0.5471428632736206</v>
+        <v>0.54714286</v>
       </c>
       <c r="AI21" s="3">
-        <v>0.6532315015792847</v>
+        <v>0.6532315</v>
       </c>
       <c r="AJ21" s="3">
-        <v>0.1534818112850189</v>
+        <v>0.15348181</v>
       </c>
       <c r="AK21" s="3">
-        <v>0.9635065793991089</v>
+        <v>0.9635066</v>
       </c>
       <c r="AL21" s="3">
-        <v>0.2718486785888672</v>
+        <v>0.27184868</v>
       </c>
       <c r="AM21" s="3">
-        <v>0.4181303977966309</v>
+        <v>0.4181304</v>
       </c>
       <c r="AN21" s="3">
-        <v>0.5721629858016968</v>
+        <v>0.572163</v>
       </c>
       <c r="AO21" s="3">
-        <v>0.5457868576049805</v>
+        <v>0.54578686</v>
       </c>
       <c r="AP21" s="3">
-        <v>0.9590633511543274</v>
+        <v>0.95906335</v>
       </c>
       <c r="AQ21" s="3">
-        <v>0.9992696642875671</v>
+        <v>0.9992696599999999</v>
       </c>
       <c r="AR21" s="3">
-        <v>0.7191826105117798</v>
+        <v>0.7191826</v>
       </c>
       <c r="AS21" s="3">
-        <v>0.8762180209159851</v>
+        <v>0.8762180000000001</v>
       </c>
       <c r="AT21" s="3">
-        <v>0.8036131858825684</v>
+        <v>0.8036132</v>
       </c>
       <c r="AU21" s="3">
-        <v>-5.433480262756348</v>
+        <v>-5.4334803</v>
       </c>
       <c r="AV21" s="3">
-        <v>88.71445465087891</v>
+        <v>88.714455</v>
       </c>
       <c r="AW21" s="3">
-        <v>15.29121208190918</v>
+        <v>15.291212</v>
       </c>
       <c r="AX21" s="3">
         <v>460.6260000000003</v>
@@ -6825,7 +6825,7 @@
         <v>14.99202021366446</v>
       </c>
       <c r="O22" s="3">
-        <v>9.017290093260467</v>
+        <v>9.017290093260469</v>
       </c>
       <c r="P22" s="3">
         <v>4.912103278568816</v>
@@ -6855,7 +6855,7 @@
         <v>-5.14467691804052</v>
       </c>
       <c r="Y22" s="3">
-        <v>7.166763644850975E-06</v>
+        <v>7.166763644850976E-06</v>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
@@ -6863,13 +6863,13 @@
         </is>
       </c>
       <c r="AA22" s="3">
-        <v>54.14443206787109</v>
+        <v>54.144432</v>
       </c>
       <c r="AB22" s="3">
-        <v>48.61449432373047</v>
+        <v>48.614494</v>
       </c>
       <c r="AC22" s="3">
-        <v>42.2707405090332</v>
+        <v>42.27074</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -6881,55 +6881,55 @@
         <v>0</v>
       </c>
       <c r="AG22" s="3">
-        <v>0.1222689375281334</v>
+        <v>0.12226894</v>
       </c>
       <c r="AH22" s="3">
-        <v>0.2155998200178146</v>
+        <v>0.21559982</v>
       </c>
       <c r="AI22" s="3">
-        <v>0.8456916809082031</v>
+        <v>0.8456917</v>
       </c>
       <c r="AJ22" s="3">
-        <v>0.06358656287193298</v>
+        <v>0.06358656</v>
       </c>
       <c r="AK22" s="3">
-        <v>0.7604100108146667</v>
+        <v>0.76041</v>
       </c>
       <c r="AL22" s="3">
-        <v>0.2809679210186005</v>
+        <v>0.28096792</v>
       </c>
       <c r="AM22" s="3">
-        <v>0.5562871694564819</v>
+        <v>0.5562871700000001</v>
       </c>
       <c r="AN22" s="3">
-        <v>0.7078112959861755</v>
+        <v>0.7078113</v>
       </c>
       <c r="AO22" s="3">
-        <v>0.05011358112096786</v>
+        <v>0.05011358</v>
       </c>
       <c r="AP22" s="3">
-        <v>0.9613454937934875</v>
+        <v>0.9613455</v>
       </c>
       <c r="AQ22" s="3">
-        <v>0.9999285936355591</v>
+        <v>0.9999285999999999</v>
       </c>
       <c r="AR22" s="3">
-        <v>0.8209439516067505</v>
+        <v>0.82094395</v>
       </c>
       <c r="AS22" s="3">
-        <v>0.968595027923584</v>
+        <v>0.968595</v>
       </c>
       <c r="AT22" s="3">
-        <v>0.7425564527511597</v>
+        <v>0.74255645</v>
       </c>
       <c r="AU22" s="3">
-        <v>-4.84219217300415</v>
+        <v>-4.842192</v>
       </c>
       <c r="AV22" s="3">
-        <v>98.20294189453125</v>
+        <v>98.20294</v>
       </c>
       <c r="AW22" s="3">
-        <v>9.877103805541992</v>
+        <v>9.877103999999999</v>
       </c>
       <c r="AX22" s="3">
         <v>405.5460000000002</v>
@@ -6997,13 +6997,13 @@
         <v>5.302380392493043</v>
       </c>
       <c r="L23" s="3">
-        <v>1.063843274589777</v>
+        <v>1.063843274589778</v>
       </c>
       <c r="M23" s="3">
         <v>0.2901128077118232</v>
       </c>
       <c r="N23" s="3">
-        <v>14.34818287521145</v>
+        <v>14.34818287521146</v>
       </c>
       <c r="O23" s="3">
         <v>8.897547764733797</v>
@@ -7044,13 +7044,13 @@
         </is>
       </c>
       <c r="AA23" s="3">
-        <v>55.36793899536133</v>
+        <v>55.36794</v>
       </c>
       <c r="AB23" s="3">
-        <v>53.72991943359375</v>
+        <v>53.72992</v>
       </c>
       <c r="AC23" s="3">
-        <v>43.53070068359375</v>
+        <v>43.5307</v>
       </c>
       <c r="AD23" s="3">
         <v>0</v>
@@ -7062,55 +7062,55 @@
         <v>0</v>
       </c>
       <c r="AG23" s="3">
-        <v>0.1413775384426117</v>
+        <v>0.14137754</v>
       </c>
       <c r="AH23" s="3">
-        <v>0.2974559664726257</v>
+        <v>0.29745597</v>
       </c>
       <c r="AI23" s="3">
-        <v>0.7128478288650513</v>
+        <v>0.7128478</v>
       </c>
       <c r="AJ23" s="3">
-        <v>0.08145667612552643</v>
+        <v>0.08145667600000001</v>
       </c>
       <c r="AK23" s="3">
-        <v>0.8391359448432922</v>
+        <v>0.83913594</v>
       </c>
       <c r="AL23" s="3">
-        <v>0.2517991065979004</v>
+        <v>0.2517991</v>
       </c>
       <c r="AM23" s="3">
-        <v>0.6325555443763733</v>
+        <v>0.63255554</v>
       </c>
       <c r="AN23" s="3">
-        <v>0.7185624837875366</v>
+        <v>0.7185625</v>
       </c>
       <c r="AO23" s="3">
-        <v>0.1633802503347397</v>
+        <v>0.16338025</v>
       </c>
       <c r="AP23" s="3">
-        <v>0.955887496471405</v>
+        <v>0.9558875</v>
       </c>
       <c r="AQ23" s="3">
-        <v>0.9997787475585938</v>
+        <v>0.99977875</v>
       </c>
       <c r="AR23" s="3">
-        <v>0.7086881399154663</v>
+        <v>0.70868814</v>
       </c>
       <c r="AS23" s="3">
-        <v>0.9530109167098999</v>
+        <v>0.9530109</v>
       </c>
       <c r="AT23" s="3">
-        <v>0.8525379300117493</v>
+        <v>0.85253793</v>
       </c>
       <c r="AU23" s="3">
-        <v>-4.67601490020752</v>
+        <v>-4.676015</v>
       </c>
       <c r="AV23" s="3">
-        <v>96.70580291748047</v>
+        <v>96.7058</v>
       </c>
       <c r="AW23" s="3">
-        <v>12.02217674255371</v>
+        <v>12.022177</v>
       </c>
       <c r="AX23" s="3">
         <v>383.5360000000002</v>
@@ -7184,7 +7184,7 @@
         <v>0.2913041082688657</v>
       </c>
       <c r="N24" s="3">
-        <v>18.99410176573746</v>
+        <v>18.99410176573745</v>
       </c>
       <c r="O24" s="3">
         <v>10.25929449369304</v>
@@ -7225,13 +7225,13 @@
         </is>
       </c>
       <c r="AA24" s="3">
-        <v>34.39155197143555</v>
+        <v>34.391552</v>
       </c>
       <c r="AB24" s="3">
-        <v>29.29227256774902</v>
+        <v>29.292273</v>
       </c>
       <c r="AC24" s="3">
-        <v>48.09518814086914</v>
+        <v>48.09519</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -7243,55 +7243,55 @@
         <v>0</v>
       </c>
       <c r="AG24" s="3">
-        <v>0.08511621505022049</v>
+        <v>0.085116215</v>
       </c>
       <c r="AH24" s="3">
-        <v>0.585709273815155</v>
+        <v>0.5857093</v>
       </c>
       <c r="AI24" s="3">
-        <v>0.725488007068634</v>
+        <v>0.725488</v>
       </c>
       <c r="AJ24" s="3">
-        <v>0.1722306907176971</v>
+        <v>0.17223069</v>
       </c>
       <c r="AK24" s="3">
-        <v>0.9519563913345337</v>
+        <v>0.9519564</v>
       </c>
       <c r="AL24" s="3">
-        <v>0.1754011809825897</v>
+        <v>0.17540118</v>
       </c>
       <c r="AM24" s="3">
-        <v>0.50825035572052</v>
+        <v>0.50825036</v>
       </c>
       <c r="AN24" s="3">
-        <v>0.7169796228408813</v>
+        <v>0.7169796000000001</v>
       </c>
       <c r="AO24" s="3">
-        <v>0.4975824952125549</v>
+        <v>0.4975825</v>
       </c>
       <c r="AP24" s="3">
-        <v>0.9634021520614624</v>
+        <v>0.96340215</v>
       </c>
       <c r="AQ24" s="3">
-        <v>0.9989982843399048</v>
+        <v>0.9989983</v>
       </c>
       <c r="AR24" s="3">
-        <v>0.7060405015945435</v>
+        <v>0.7060405</v>
       </c>
       <c r="AS24" s="3">
-        <v>0.8325538635253906</v>
+        <v>0.83255386</v>
       </c>
       <c r="AT24" s="3">
-        <v>0.8729203343391418</v>
+        <v>0.87292033</v>
       </c>
       <c r="AU24" s="3">
-        <v>-5.34190559387207</v>
+        <v>-5.3419056</v>
       </c>
       <c r="AV24" s="3">
-        <v>94.22610473632812</v>
+        <v>94.226105</v>
       </c>
       <c r="AW24" s="3">
-        <v>14.56496429443359</v>
+        <v>14.564964</v>
       </c>
       <c r="AX24" s="3">
         <v>475.6370000000003</v>
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="AA25" s="3">
-        <v>49.44774627685547</v>
+        <v>49.447746</v>
       </c>
       <c r="AB25" s="3">
-        <v>28.99290084838867</v>
+        <v>28.9929</v>
       </c>
       <c r="AC25" s="3">
-        <v>45.80880737304688</v>
+        <v>45.808807</v>
       </c>
       <c r="AD25" s="3">
         <v>0</v>
@@ -7424,55 +7424,55 @@
         <v>0</v>
       </c>
       <c r="AG25" s="3">
-        <v>0.5530637502670288</v>
+        <v>0.55306375</v>
       </c>
       <c r="AH25" s="3">
-        <v>0.3513157367706299</v>
+        <v>0.35131574</v>
       </c>
       <c r="AI25" s="3">
-        <v>0.9046971201896667</v>
+        <v>0.9046971</v>
       </c>
       <c r="AJ25" s="3">
-        <v>0.07876376807689667</v>
+        <v>0.07876377</v>
       </c>
       <c r="AK25" s="3">
-        <v>0.9365013837814331</v>
+        <v>0.9365014</v>
       </c>
       <c r="AL25" s="3">
-        <v>0.3686340749263763</v>
+        <v>0.36863407</v>
       </c>
       <c r="AM25" s="3">
-        <v>0.8324984312057495</v>
+        <v>0.83249843</v>
       </c>
       <c r="AN25" s="3">
-        <v>0.8911569714546204</v>
+        <v>0.891157</v>
       </c>
       <c r="AO25" s="3">
-        <v>0.229658916592598</v>
+        <v>0.22965892</v>
       </c>
       <c r="AP25" s="3">
-        <v>0.9842985868453979</v>
+        <v>0.9842986</v>
       </c>
       <c r="AQ25" s="3">
-        <v>0.9999605417251587</v>
+        <v>0.99996054</v>
       </c>
       <c r="AR25" s="3">
-        <v>0.683569073677063</v>
+        <v>0.6835691</v>
       </c>
       <c r="AS25" s="3">
-        <v>0.9552294611930847</v>
+        <v>0.95522946</v>
       </c>
       <c r="AT25" s="3">
-        <v>0.9588723182678223</v>
+        <v>0.9588723</v>
       </c>
       <c r="AU25" s="3">
-        <v>-5.105210304260254</v>
+        <v>-5.1052103</v>
       </c>
       <c r="AV25" s="3">
-        <v>102.3317565917969</v>
+        <v>102.33176</v>
       </c>
       <c r="AW25" s="3">
-        <v>5.011994361877441</v>
+        <v>5.0119944</v>
       </c>
       <c r="AX25" s="3">
         <v>469.5930000000002</v>
@@ -7579,7 +7579,7 @@
         <v>-5.14467691804052</v>
       </c>
       <c r="Y26" s="3">
-        <v>7.166763644850975E-06</v>
+        <v>7.166763644850976E-06</v>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
@@ -7587,13 +7587,13 @@
         </is>
       </c>
       <c r="AA26" s="3">
-        <v>62.84810256958008</v>
+        <v>62.848103</v>
       </c>
       <c r="AB26" s="3">
-        <v>55.03955078125</v>
+        <v>55.03955</v>
       </c>
       <c r="AC26" s="3">
-        <v>48.48752212524414</v>
+        <v>48.487522</v>
       </c>
       <c r="AD26" s="3">
         <v>0</v>
@@ -7605,55 +7605,55 @@
         <v>0</v>
       </c>
       <c r="AG26" s="3">
-        <v>0.1596864461898804</v>
+        <v>0.15968645</v>
       </c>
       <c r="AH26" s="3">
-        <v>0.2792691588401794</v>
+        <v>0.27926916</v>
       </c>
       <c r="AI26" s="3">
-        <v>0.8238638043403625</v>
+        <v>0.8238638</v>
       </c>
       <c r="AJ26" s="3">
-        <v>0.05655995756387711</v>
+        <v>0.056559958</v>
       </c>
       <c r="AK26" s="3">
-        <v>0.865709125995636</v>
+        <v>0.8657091</v>
       </c>
       <c r="AL26" s="3">
-        <v>0.4318308234214783</v>
+        <v>0.43183082</v>
       </c>
       <c r="AM26" s="3">
-        <v>0.7112659215927124</v>
+        <v>0.7112659</v>
       </c>
       <c r="AN26" s="3">
-        <v>0.8083459734916687</v>
+        <v>0.808346</v>
       </c>
       <c r="AO26" s="3">
-        <v>0.1134422272443771</v>
+        <v>0.11344223</v>
       </c>
       <c r="AP26" s="3">
-        <v>0.987573504447937</v>
+        <v>0.9875735</v>
       </c>
       <c r="AQ26" s="3">
-        <v>0.9999877214431763</v>
+        <v>0.9999877</v>
       </c>
       <c r="AR26" s="3">
-        <v>0.7667804956436157</v>
+        <v>0.7667805</v>
       </c>
       <c r="AS26" s="3">
-        <v>0.9786069989204407</v>
+        <v>0.978607</v>
       </c>
       <c r="AT26" s="3">
-        <v>0.8238350749015808</v>
+        <v>0.8238351</v>
       </c>
       <c r="AU26" s="3">
-        <v>-4.787118434906006</v>
+        <v>-4.7871184</v>
       </c>
       <c r="AV26" s="3">
-        <v>99.26639556884766</v>
+        <v>99.266396</v>
       </c>
       <c r="AW26" s="3">
-        <v>10.56526756286621</v>
+        <v>10.565268</v>
       </c>
       <c r="AX26" s="3">
         <v>405.5460000000002</v>
@@ -7724,7 +7724,7 @@
         <v>1.164876168654569</v>
       </c>
       <c r="M27" s="3">
-        <v>0.3027107069978566</v>
+        <v>0.3027107069978565</v>
       </c>
       <c r="N27" s="3">
         <v>18.23776790244059</v>
@@ -7736,7 +7736,7 @@
         <v>4.835123831345431</v>
       </c>
       <c r="Q27" s="3">
-        <v>0.3027107069978566</v>
+        <v>0.3027107069978565</v>
       </c>
       <c r="R27" s="3">
         <v>3.728749283678181</v>
@@ -7751,7 +7751,7 @@
         <v>5.42843681706123</v>
       </c>
       <c r="V27" s="3">
-        <v>0.3027107069978566</v>
+        <v>0.3027107069978565</v>
       </c>
       <c r="W27" s="3">
         <v>3.403400000000001</v>
@@ -7768,13 +7768,13 @@
         </is>
       </c>
       <c r="AA27" s="3">
-        <v>43.70171356201172</v>
+        <v>43.701714</v>
       </c>
       <c r="AB27" s="3">
-        <v>27.25896263122559</v>
+        <v>27.258963</v>
       </c>
       <c r="AC27" s="3">
-        <v>48.61517333984375</v>
+        <v>48.615173</v>
       </c>
       <c r="AD27" s="3">
         <v>0</v>
@@ -7786,55 +7786,55 @@
         <v>0</v>
       </c>
       <c r="AG27" s="3">
-        <v>0.05936180800199509</v>
+        <v>0.059361808</v>
       </c>
       <c r="AH27" s="3">
-        <v>0.2590552270412445</v>
+        <v>0.25905523</v>
       </c>
       <c r="AI27" s="3">
-        <v>0.8956759572029114</v>
+        <v>0.89567596</v>
       </c>
       <c r="AJ27" s="3">
-        <v>0.1856918931007385</v>
+        <v>0.1856919</v>
       </c>
       <c r="AK27" s="3">
-        <v>0.7018319964408875</v>
+        <v>0.701832</v>
       </c>
       <c r="AL27" s="3">
-        <v>0.06777338683605194</v>
+        <v>0.06777339</v>
       </c>
       <c r="AM27" s="3">
-        <v>0.2325942516326904</v>
+        <v>0.23259425</v>
       </c>
       <c r="AN27" s="3">
-        <v>0.6252275109291077</v>
+        <v>0.6252275</v>
       </c>
       <c r="AO27" s="3">
-        <v>0.1200999021530151</v>
+        <v>0.1200999</v>
       </c>
       <c r="AP27" s="3">
-        <v>0.9302724003791809</v>
+        <v>0.9302724</v>
       </c>
       <c r="AQ27" s="3">
-        <v>0.9975115060806274</v>
+        <v>0.9975115</v>
       </c>
       <c r="AR27" s="3">
-        <v>0.8354297876358032</v>
+        <v>0.8354298</v>
       </c>
       <c r="AS27" s="3">
-        <v>0.8230787515640259</v>
+        <v>0.82307875</v>
       </c>
       <c r="AT27" s="3">
-        <v>0.7909396886825562</v>
+        <v>0.7909397</v>
       </c>
       <c r="AU27" s="3">
-        <v>-5.250341892242432</v>
+        <v>-5.250342</v>
       </c>
       <c r="AV27" s="3">
-        <v>96.24810791015625</v>
+        <v>96.24811</v>
       </c>
       <c r="AW27" s="3">
-        <v>6.668381690979004</v>
+        <v>6.6683817</v>
       </c>
       <c r="AX27" s="3">
         <v>480.6340000000002</v>
@@ -7949,13 +7949,13 @@
         </is>
       </c>
       <c r="AA28" s="3">
-        <v>36.80594635009766</v>
+        <v>36.805946</v>
       </c>
       <c r="AB28" s="3">
-        <v>33.49628448486328</v>
+        <v>33.496284</v>
       </c>
       <c r="AC28" s="3">
-        <v>46.93061447143555</v>
+        <v>46.930614</v>
       </c>
       <c r="AD28" s="3">
         <v>0</v>
@@ -7967,55 +7967,55 @@
         <v>0</v>
       </c>
       <c r="AG28" s="3">
-        <v>0.07718510180711746</v>
+        <v>0.07718510000000001</v>
       </c>
       <c r="AH28" s="3">
-        <v>0.5636357069015503</v>
+        <v>0.5636357</v>
       </c>
       <c r="AI28" s="3">
-        <v>0.7042747735977173</v>
+        <v>0.7042748</v>
       </c>
       <c r="AJ28" s="3">
-        <v>0.1850818693637848</v>
+        <v>0.18508187</v>
       </c>
       <c r="AK28" s="3">
-        <v>0.9314249753952026</v>
+        <v>0.9314249999999999</v>
       </c>
       <c r="AL28" s="3">
-        <v>0.1184100657701492</v>
+        <v>0.118410066</v>
       </c>
       <c r="AM28" s="3">
-        <v>0.4158545434474945</v>
+        <v>0.41585454</v>
       </c>
       <c r="AN28" s="3">
-        <v>0.64786297082901</v>
+        <v>0.647863</v>
       </c>
       <c r="AO28" s="3">
-        <v>0.431628942489624</v>
+        <v>0.43162894</v>
       </c>
       <c r="AP28" s="3">
-        <v>0.9296684265136719</v>
+        <v>0.9296684</v>
       </c>
       <c r="AQ28" s="3">
-        <v>0.9976919889450073</v>
+        <v>0.997692</v>
       </c>
       <c r="AR28" s="3">
-        <v>0.71753990650177</v>
+        <v>0.7175399</v>
       </c>
       <c r="AS28" s="3">
-        <v>0.8071349859237671</v>
+        <v>0.807135</v>
       </c>
       <c r="AT28" s="3">
-        <v>0.83851557970047</v>
+        <v>0.8385156</v>
       </c>
       <c r="AU28" s="3">
-        <v>-5.296712398529053</v>
+        <v>-5.2967124</v>
       </c>
       <c r="AV28" s="3">
-        <v>95.38169860839844</v>
+        <v>95.3817</v>
       </c>
       <c r="AW28" s="3">
-        <v>14.22715950012207</v>
+        <v>14.2271595</v>
       </c>
       <c r="AX28" s="3">
         <v>475.6370000000003</v>
@@ -8089,7 +8089,7 @@
         <v>0.305427286047331</v>
       </c>
       <c r="N29" s="3">
-        <v>19.03384206919266</v>
+        <v>19.03384206919267</v>
       </c>
       <c r="O29" s="3">
         <v>9.862357491641434</v>
@@ -8116,7 +8116,7 @@
         <v>0.305427286047331</v>
       </c>
       <c r="W29" s="3">
-        <v>3.290500000000002</v>
+        <v>3.290500000000001</v>
       </c>
       <c r="X29" s="3">
         <v>-5.403973534407199</v>
@@ -8130,13 +8130,13 @@
         </is>
       </c>
       <c r="AA29" s="3">
-        <v>56.17996978759766</v>
+        <v>56.17997</v>
       </c>
       <c r="AB29" s="3">
-        <v>47.58806610107422</v>
+        <v>47.588066</v>
       </c>
       <c r="AC29" s="3">
-        <v>41.54888534545898</v>
+        <v>41.548885</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -8148,61 +8148,61 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
-        <v>0.2855882942676544</v>
+        <v>0.2855883</v>
       </c>
       <c r="AH29" s="3">
-        <v>0.3612461686134338</v>
+        <v>0.36124617</v>
       </c>
       <c r="AI29" s="3">
-        <v>0.858685314655304</v>
+        <v>0.8586853</v>
       </c>
       <c r="AJ29" s="3">
-        <v>0.08441390097141266</v>
+        <v>0.0844139</v>
       </c>
       <c r="AK29" s="3">
-        <v>0.9224992990493774</v>
+        <v>0.9224993</v>
       </c>
       <c r="AL29" s="3">
-        <v>0.4540093541145325</v>
+        <v>0.45400935</v>
       </c>
       <c r="AM29" s="3">
-        <v>0.7599788904190063</v>
+        <v>0.7599789</v>
       </c>
       <c r="AN29" s="3">
-        <v>0.8951212763786316</v>
+        <v>0.8951213</v>
       </c>
       <c r="AO29" s="3">
-        <v>0.2079469859600067</v>
+        <v>0.20794699</v>
       </c>
       <c r="AP29" s="3">
-        <v>0.9832882881164551</v>
+        <v>0.9832883</v>
       </c>
       <c r="AQ29" s="3">
-        <v>0.9999605417251587</v>
+        <v>0.99996054</v>
       </c>
       <c r="AR29" s="3">
-        <v>0.6704878807067871</v>
+        <v>0.6704879</v>
       </c>
       <c r="AS29" s="3">
-        <v>0.9544416666030884</v>
+        <v>0.95444167</v>
       </c>
       <c r="AT29" s="3">
-        <v>0.9488126635551453</v>
+        <v>0.94881266</v>
       </c>
       <c r="AU29" s="3">
-        <v>-4.889243125915527</v>
+        <v>-4.889243</v>
       </c>
       <c r="AV29" s="3">
-        <v>103.2105255126953</v>
+        <v>103.210526</v>
       </c>
       <c r="AW29" s="3">
-        <v>5.028652191162109</v>
+        <v>5.028652</v>
       </c>
       <c r="AX29" s="3">
         <v>468.6010000000002</v>
       </c>
       <c r="AY29" s="3">
-        <v>3.290500000000002</v>
+        <v>3.290500000000001</v>
       </c>
       <c r="AZ29" s="3">
         <v>0.4823243859287882</v>
@@ -8311,13 +8311,13 @@
         </is>
       </c>
       <c r="AA30" s="3">
-        <v>46.09317779541016</v>
+        <v>46.093178</v>
       </c>
       <c r="AB30" s="3">
-        <v>29.86197471618652</v>
+        <v>29.861975</v>
       </c>
       <c r="AC30" s="3">
-        <v>46.98077392578125</v>
+        <v>46.980774</v>
       </c>
       <c r="AD30" s="3">
         <v>0</v>
@@ -8329,55 +8329,55 @@
         <v>0</v>
       </c>
       <c r="AG30" s="3">
-        <v>0.05244184285402298</v>
+        <v>0.052441843</v>
       </c>
       <c r="AH30" s="3">
-        <v>0.2689527869224548</v>
+        <v>0.2689528</v>
       </c>
       <c r="AI30" s="3">
-        <v>0.8882083892822266</v>
+        <v>0.8882084</v>
       </c>
       <c r="AJ30" s="3">
-        <v>0.1587379723787308</v>
+        <v>0.15873797</v>
       </c>
       <c r="AK30" s="3">
-        <v>0.7801658511161804</v>
+        <v>0.78016585</v>
       </c>
       <c r="AL30" s="3">
-        <v>0.1343093663454056</v>
+        <v>0.13430937</v>
       </c>
       <c r="AM30" s="3">
-        <v>0.3375517725944519</v>
+        <v>0.33755177</v>
       </c>
       <c r="AN30" s="3">
-        <v>0.7266050577163696</v>
+        <v>0.72660506</v>
       </c>
       <c r="AO30" s="3">
-        <v>0.1580548286437988</v>
+        <v>0.15805483</v>
       </c>
       <c r="AP30" s="3">
-        <v>0.969207763671875</v>
+        <v>0.96920776</v>
       </c>
       <c r="AQ30" s="3">
-        <v>0.9994207620620728</v>
+        <v>0.99942076</v>
       </c>
       <c r="AR30" s="3">
-        <v>0.8170819282531738</v>
+        <v>0.8170819</v>
       </c>
       <c r="AS30" s="3">
-        <v>0.8903955221176147</v>
+        <v>0.8903955</v>
       </c>
       <c r="AT30" s="3">
-        <v>0.8408457040786743</v>
+        <v>0.8408457</v>
       </c>
       <c r="AU30" s="3">
-        <v>-5.230033874511719</v>
+        <v>-5.230034</v>
       </c>
       <c r="AV30" s="3">
-        <v>96.63436126708984</v>
+        <v>96.63436</v>
       </c>
       <c r="AW30" s="3">
-        <v>6.228826999664307</v>
+        <v>6.228827</v>
       </c>
       <c r="AX30" s="3">
         <v>480.6340000000002</v>
@@ -8492,13 +8492,13 @@
         </is>
       </c>
       <c r="AA31" s="3">
-        <v>42.58502578735352</v>
+        <v>42.585026</v>
       </c>
       <c r="AB31" s="3">
-        <v>41.90291976928711</v>
+        <v>41.90292</v>
       </c>
       <c r="AC31" s="3">
-        <v>41.77748107910156</v>
+        <v>41.77748</v>
       </c>
       <c r="AD31" s="3">
         <v>0</v>
@@ -8510,55 +8510,55 @@
         <v>0</v>
       </c>
       <c r="AG31" s="3">
-        <v>0.06033305078744888</v>
+        <v>0.06033305</v>
       </c>
       <c r="AH31" s="3">
-        <v>0.241472452878952</v>
+        <v>0.24147245</v>
       </c>
       <c r="AI31" s="3">
-        <v>0.8612071871757507</v>
+        <v>0.8612072</v>
       </c>
       <c r="AJ31" s="3">
-        <v>0.07321158796548843</v>
+        <v>0.07321158999999999</v>
       </c>
       <c r="AK31" s="3">
-        <v>0.799024224281311</v>
+        <v>0.7990242</v>
       </c>
       <c r="AL31" s="3">
-        <v>0.3796192705631256</v>
+        <v>0.37961927</v>
       </c>
       <c r="AM31" s="3">
-        <v>0.7487787008285522</v>
+        <v>0.7487787</v>
       </c>
       <c r="AN31" s="3">
-        <v>0.8879830241203308</v>
+        <v>0.887983</v>
       </c>
       <c r="AO31" s="3">
-        <v>0.1368885934352875</v>
+        <v>0.1368886</v>
       </c>
       <c r="AP31" s="3">
-        <v>0.9806154370307922</v>
+        <v>0.98061544</v>
       </c>
       <c r="AQ31" s="3">
-        <v>0.9998500943183899</v>
+        <v>0.9998501</v>
       </c>
       <c r="AR31" s="3">
-        <v>0.7418175935745239</v>
+        <v>0.7418176</v>
       </c>
       <c r="AS31" s="3">
-        <v>0.9368144273757935</v>
+        <v>0.9368144</v>
       </c>
       <c r="AT31" s="3">
-        <v>0.7687383890151978</v>
+        <v>0.7687384</v>
       </c>
       <c r="AU31" s="3">
-        <v>-4.910858154296875</v>
+        <v>-4.910858</v>
       </c>
       <c r="AV31" s="3">
-        <v>99.51468658447266</v>
+        <v>99.51469</v>
       </c>
       <c r="AW31" s="3">
-        <v>9.36732006072998</v>
+        <v>9.367319999999999</v>
       </c>
       <c r="AX31" s="3">
         <v>391.5190000000001</v>
@@ -8673,13 +8673,13 @@
         </is>
       </c>
       <c r="AA32" s="3">
-        <v>40.37352752685547</v>
+        <v>40.373528</v>
       </c>
       <c r="AB32" s="3">
-        <v>37.10095977783203</v>
+        <v>37.10096</v>
       </c>
       <c r="AC32" s="3">
-        <v>41.42470932006836</v>
+        <v>41.42471</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
@@ -8691,55 +8691,55 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
-        <v>0.1258212029933929</v>
+        <v>0.1258212</v>
       </c>
       <c r="AH32" s="3">
-        <v>0.430647999048233</v>
+        <v>0.430648</v>
       </c>
       <c r="AI32" s="3">
-        <v>0.6815851330757141</v>
+        <v>0.68158513</v>
       </c>
       <c r="AJ32" s="3">
-        <v>0.1227786988019943</v>
+        <v>0.1227787</v>
       </c>
       <c r="AK32" s="3">
-        <v>0.9147694706916809</v>
+        <v>0.9147695</v>
       </c>
       <c r="AL32" s="3">
-        <v>0.1529637724161148</v>
+        <v>0.15296377</v>
       </c>
       <c r="AM32" s="3">
-        <v>0.4958227276802063</v>
+        <v>0.49582273</v>
       </c>
       <c r="AN32" s="3">
-        <v>0.6837601065635681</v>
+        <v>0.6837601</v>
       </c>
       <c r="AO32" s="3">
-        <v>0.3408937454223633</v>
+        <v>0.34089375</v>
       </c>
       <c r="AP32" s="3">
-        <v>0.963294506072998</v>
+        <v>0.9632945000000001</v>
       </c>
       <c r="AQ32" s="3">
-        <v>0.9990781545639038</v>
+        <v>0.99907815</v>
       </c>
       <c r="AR32" s="3">
-        <v>0.6971748471260071</v>
+        <v>0.69717485</v>
       </c>
       <c r="AS32" s="3">
-        <v>0.8226183652877808</v>
+        <v>0.82261837</v>
       </c>
       <c r="AT32" s="3">
-        <v>0.7534968256950378</v>
+        <v>0.7534968</v>
       </c>
       <c r="AU32" s="3">
-        <v>-5.157549381256104</v>
+        <v>-5.1575494</v>
       </c>
       <c r="AV32" s="3">
-        <v>98.61801147460938</v>
+        <v>98.61801</v>
       </c>
       <c r="AW32" s="3">
-        <v>9.65245532989502</v>
+        <v>9.652455</v>
       </c>
       <c r="AX32" s="3">
         <v>420.5610000000002</v>
@@ -8854,13 +8854,13 @@
         </is>
       </c>
       <c r="AA33" s="3">
-        <v>46.97864151000977</v>
+        <v>46.97864</v>
       </c>
       <c r="AB33" s="3">
-        <v>40.24519729614258</v>
+        <v>40.245197</v>
       </c>
       <c r="AC33" s="3">
-        <v>46.63026809692383</v>
+        <v>46.63027</v>
       </c>
       <c r="AD33" s="3">
         <v>0</v>
@@ -8872,55 +8872,55 @@
         <v>0</v>
       </c>
       <c r="AG33" s="3">
-        <v>0.2830462455749512</v>
+        <v>0.28304625</v>
       </c>
       <c r="AH33" s="3">
-        <v>0.2151418626308441</v>
+        <v>0.21514186</v>
       </c>
       <c r="AI33" s="3">
-        <v>0.4728532731533051</v>
+        <v>0.47285327</v>
       </c>
       <c r="AJ33" s="3">
-        <v>0.1956559419631958</v>
+        <v>0.19565594</v>
       </c>
       <c r="AK33" s="3">
-        <v>0.7975501418113708</v>
+        <v>0.79755014</v>
       </c>
       <c r="AL33" s="3">
-        <v>0.07092715054750443</v>
+        <v>0.07092714999999999</v>
       </c>
       <c r="AM33" s="3">
-        <v>0.2129030674695969</v>
+        <v>0.21290307</v>
       </c>
       <c r="AN33" s="3">
-        <v>0.2200562208890915</v>
+        <v>0.22005622</v>
       </c>
       <c r="AO33" s="3">
-        <v>0.3056006729602814</v>
+        <v>0.30560067</v>
       </c>
       <c r="AP33" s="3">
-        <v>0.6399297118186951</v>
+        <v>0.6399297</v>
       </c>
       <c r="AQ33" s="3">
-        <v>0.5382658839225769</v>
+        <v>0.5382659</v>
       </c>
       <c r="AR33" s="3">
-        <v>0.4667628407478333</v>
+        <v>0.46676284</v>
       </c>
       <c r="AS33" s="3">
-        <v>0.2649660110473633</v>
+        <v>0.264966</v>
       </c>
       <c r="AT33" s="3">
-        <v>0.4897471368312836</v>
+        <v>0.48974714</v>
       </c>
       <c r="AU33" s="3">
-        <v>-4.92802906036377</v>
+        <v>-4.928029</v>
       </c>
       <c r="AV33" s="3">
-        <v>95.23081970214844</v>
+        <v>95.23081999999999</v>
       </c>
       <c r="AW33" s="3">
-        <v>13.71837043762207</v>
+        <v>13.71837</v>
       </c>
       <c r="AX33" s="3">
         <v>445.5870000000003</v>
@@ -9035,13 +9035,13 @@
         </is>
       </c>
       <c r="AA34" s="3">
-        <v>37.41826629638672</v>
+        <v>37.418266</v>
       </c>
       <c r="AB34" s="3">
-        <v>25.54359817504883</v>
+        <v>25.543598</v>
       </c>
       <c r="AC34" s="3">
-        <v>41.66534423828125</v>
+        <v>41.665344</v>
       </c>
       <c r="AD34" s="3">
         <v>0</v>
@@ -9053,55 +9053,55 @@
         <v>0</v>
       </c>
       <c r="AG34" s="3">
-        <v>0.1102207079529762</v>
+        <v>0.11022071</v>
       </c>
       <c r="AH34" s="3">
-        <v>0.3185543417930603</v>
+        <v>0.31855434</v>
       </c>
       <c r="AI34" s="3">
-        <v>0.801439642906189</v>
+        <v>0.80143964</v>
       </c>
       <c r="AJ34" s="3">
-        <v>0.0750899612903595</v>
+        <v>0.07508996</v>
       </c>
       <c r="AK34" s="3">
-        <v>0.7865921854972839</v>
+        <v>0.7865922</v>
       </c>
       <c r="AL34" s="3">
-        <v>0.01920044422149658</v>
+        <v>0.019200444</v>
       </c>
       <c r="AM34" s="3">
-        <v>0.2639109492301941</v>
+        <v>0.26391095</v>
       </c>
       <c r="AN34" s="3">
-        <v>0.5285186171531677</v>
+        <v>0.5285185999999999</v>
       </c>
       <c r="AO34" s="3">
-        <v>0.0845082625746727</v>
+        <v>0.08450826</v>
       </c>
       <c r="AP34" s="3">
-        <v>0.9487897157669067</v>
+        <v>0.9487897</v>
       </c>
       <c r="AQ34" s="3">
-        <v>0.9978746175765991</v>
+        <v>0.9978745999999999</v>
       </c>
       <c r="AR34" s="3">
-        <v>0.7399321794509888</v>
+        <v>0.7399322</v>
       </c>
       <c r="AS34" s="3">
-        <v>0.8025595545768738</v>
+        <v>0.80255955</v>
       </c>
       <c r="AT34" s="3">
-        <v>0.8492690324783325</v>
+        <v>0.84926903</v>
       </c>
       <c r="AU34" s="3">
-        <v>-5.150025844573975</v>
+        <v>-5.150026</v>
       </c>
       <c r="AV34" s="3">
-        <v>96.41035461425781</v>
+        <v>96.410355</v>
       </c>
       <c r="AW34" s="3">
-        <v>10.68796253204346</v>
+        <v>10.687963</v>
       </c>
       <c r="AX34" s="3">
         <v>502.6590000000003</v>
@@ -9172,7 +9172,7 @@
         <v>1.079468375006204</v>
       </c>
       <c r="M35" s="3">
-        <v>0.3217725868544301</v>
+        <v>0.32177258685443</v>
       </c>
       <c r="N35" s="3">
         <v>15.62167558534073</v>
@@ -9184,7 +9184,7 @@
         <v>4.920531624993796</v>
       </c>
       <c r="Q35" s="3">
-        <v>0.3217725868544301</v>
+        <v>0.32177258685443</v>
       </c>
       <c r="R35" s="3">
         <v>2.810568048679361</v>
@@ -9199,7 +9199,7 @@
         <v>5.551205895228478</v>
       </c>
       <c r="V35" s="3">
-        <v>0.3217725868544301</v>
+        <v>0.32177258685443</v>
       </c>
       <c r="W35" s="3">
         <v>3.0899</v>
@@ -9216,13 +9216,13 @@
         </is>
       </c>
       <c r="AA35" s="3">
-        <v>24.42134475708008</v>
+        <v>24.421345</v>
       </c>
       <c r="AB35" s="3">
-        <v>13.3554105758667</v>
+        <v>13.355411</v>
       </c>
       <c r="AC35" s="3">
-        <v>53.5404052734375</v>
+        <v>53.540405</v>
       </c>
       <c r="AD35" s="3">
         <v>0</v>
@@ -9234,55 +9234,55 @@
         <v>1</v>
       </c>
       <c r="AG35" s="3">
-        <v>0.1385819613933563</v>
+        <v>0.13858196</v>
       </c>
       <c r="AH35" s="3">
-        <v>0.4566910862922668</v>
+        <v>0.4566911</v>
       </c>
       <c r="AI35" s="3">
-        <v>0.5648061633110046</v>
+        <v>0.5648061599999999</v>
       </c>
       <c r="AJ35" s="3">
-        <v>0.1457886397838593</v>
+        <v>0.14578864</v>
       </c>
       <c r="AK35" s="3">
-        <v>0.9624167680740356</v>
+        <v>0.96241677</v>
       </c>
       <c r="AL35" s="3">
-        <v>0.2665676176548004</v>
+        <v>0.26656762</v>
       </c>
       <c r="AM35" s="3">
-        <v>0.4469286501407623</v>
+        <v>0.44692865</v>
       </c>
       <c r="AN35" s="3">
-        <v>0.5707305669784546</v>
+        <v>0.57073057</v>
       </c>
       <c r="AO35" s="3">
-        <v>0.5741319060325623</v>
+        <v>0.5741319</v>
       </c>
       <c r="AP35" s="3">
-        <v>0.9509831666946411</v>
+        <v>0.95098317</v>
       </c>
       <c r="AQ35" s="3">
-        <v>0.9984723925590515</v>
+        <v>0.9984724</v>
       </c>
       <c r="AR35" s="3">
-        <v>0.6445173025131226</v>
+        <v>0.6445173</v>
       </c>
       <c r="AS35" s="3">
-        <v>0.8511065244674683</v>
+        <v>0.8511065</v>
       </c>
       <c r="AT35" s="3">
-        <v>0.8045284152030945</v>
+        <v>0.8045284</v>
       </c>
       <c r="AU35" s="3">
-        <v>-5.522937297821045</v>
+        <v>-5.5229373</v>
       </c>
       <c r="AV35" s="3">
-        <v>89.66946411132812</v>
+        <v>89.669464</v>
       </c>
       <c r="AW35" s="3">
-        <v>17.23914527893066</v>
+        <v>17.239145</v>
       </c>
       <c r="AX35" s="3">
         <v>448.6150000000002</v>
@@ -9397,13 +9397,13 @@
         </is>
       </c>
       <c r="AA36" s="3">
-        <v>56.0643424987793</v>
+        <v>56.064342</v>
       </c>
       <c r="AB36" s="3">
-        <v>37.55717086791992</v>
+        <v>37.55717</v>
       </c>
       <c r="AC36" s="3">
-        <v>44.97119903564453</v>
+        <v>44.9712</v>
       </c>
       <c r="AD36" s="3">
         <v>0</v>
@@ -9415,55 +9415,55 @@
         <v>0</v>
       </c>
       <c r="AG36" s="3">
-        <v>0.02980236150324345</v>
+        <v>0.029802362</v>
       </c>
       <c r="AH36" s="3">
-        <v>0.3637968897819519</v>
+        <v>0.3637969</v>
       </c>
       <c r="AI36" s="3">
-        <v>0.8479196429252625</v>
+        <v>0.84791964</v>
       </c>
       <c r="AJ36" s="3">
-        <v>0.04437246918678284</v>
+        <v>0.04437247</v>
       </c>
       <c r="AK36" s="3">
-        <v>0.9465765953063965</v>
+        <v>0.9465766</v>
       </c>
       <c r="AL36" s="3">
-        <v>0.4215923249721527</v>
+        <v>0.42159232</v>
       </c>
       <c r="AM36" s="3">
-        <v>0.8637058138847351</v>
+        <v>0.8637058</v>
       </c>
       <c r="AN36" s="3">
-        <v>0.9460177421569824</v>
+        <v>0.9460177400000001</v>
       </c>
       <c r="AO36" s="3">
-        <v>0.2779960036277771</v>
+        <v>0.277996</v>
       </c>
       <c r="AP36" s="3">
-        <v>0.9977461695671082</v>
+        <v>0.99774617</v>
       </c>
       <c r="AQ36" s="3">
-        <v>0.9999968409538269</v>
+        <v>0.99999684</v>
       </c>
       <c r="AR36" s="3">
-        <v>0.6990081667900085</v>
+        <v>0.69900817</v>
       </c>
       <c r="AS36" s="3">
-        <v>0.9694300889968872</v>
+        <v>0.9694301</v>
       </c>
       <c r="AT36" s="3">
-        <v>0.895953357219696</v>
+        <v>0.89595336</v>
       </c>
       <c r="AU36" s="3">
-        <v>-4.98690128326416</v>
+        <v>-4.9869013</v>
       </c>
       <c r="AV36" s="3">
-        <v>99.67478179931641</v>
+        <v>99.67478</v>
       </c>
       <c r="AW36" s="3">
-        <v>9.079287528991699</v>
+        <v>9.079288</v>
       </c>
       <c r="AX36" s="3">
         <v>458.6100000000002</v>
@@ -9534,7 +9534,7 @@
         <v>1.161457990644526</v>
       </c>
       <c r="M37" s="3">
-        <v>0.3282329990984869</v>
+        <v>0.3282329990984868</v>
       </c>
       <c r="N37" s="3">
         <v>18.70125795773799</v>
@@ -9546,7 +9546,7 @@
         <v>4.838542009355473</v>
       </c>
       <c r="Q37" s="3">
-        <v>0.3282329990984869</v>
+        <v>0.3282329990984868</v>
       </c>
       <c r="R37" s="3">
         <v>3.297017956274544</v>
@@ -9561,7 +9561,7 @@
         <v>5.481878687588508</v>
       </c>
       <c r="V37" s="3">
-        <v>0.3282329990984869</v>
+        <v>0.3282329990984868</v>
       </c>
       <c r="W37" s="3">
         <v>2.3663</v>
@@ -9578,13 +9578,13 @@
         </is>
       </c>
       <c r="AA37" s="3">
-        <v>42.92306900024414</v>
+        <v>42.92307</v>
       </c>
       <c r="AB37" s="3">
-        <v>42.75831604003906</v>
+        <v>42.758316</v>
       </c>
       <c r="AC37" s="3">
-        <v>41.326416015625</v>
+        <v>41.326416</v>
       </c>
       <c r="AD37" s="3">
         <v>0</v>
@@ -9596,55 +9596,55 @@
         <v>0</v>
       </c>
       <c r="AG37" s="3">
-        <v>0.3005689978599548</v>
+        <v>0.300569</v>
       </c>
       <c r="AH37" s="3">
-        <v>0.4723905622959137</v>
+        <v>0.47239056</v>
       </c>
       <c r="AI37" s="3">
-        <v>0.5627854466438293</v>
+        <v>0.56278545</v>
       </c>
       <c r="AJ37" s="3">
-        <v>0.09477584064006805</v>
+        <v>0.09477584</v>
       </c>
       <c r="AK37" s="3">
-        <v>0.8845173120498657</v>
+        <v>0.8845173</v>
       </c>
       <c r="AL37" s="3">
-        <v>0.04209594056010246</v>
+        <v>0.04209594</v>
       </c>
       <c r="AM37" s="3">
-        <v>0.3050220906734467</v>
+        <v>0.3050221</v>
       </c>
       <c r="AN37" s="3">
-        <v>0.3915960192680359</v>
+        <v>0.39159602</v>
       </c>
       <c r="AO37" s="3">
-        <v>0.2195128500461578</v>
+        <v>0.21951285</v>
       </c>
       <c r="AP37" s="3">
-        <v>0.8970651626586914</v>
+        <v>0.89706516</v>
       </c>
       <c r="AQ37" s="3">
-        <v>0.9962860941886902</v>
+        <v>0.9962861</v>
       </c>
       <c r="AR37" s="3">
-        <v>0.6391496062278748</v>
+        <v>0.6391496</v>
       </c>
       <c r="AS37" s="3">
-        <v>0.8414341807365417</v>
+        <v>0.8414342</v>
       </c>
       <c r="AT37" s="3">
-        <v>0.766788125038147</v>
+        <v>0.7667881</v>
       </c>
       <c r="AU37" s="3">
-        <v>-4.975938320159912</v>
+        <v>-4.9759383</v>
       </c>
       <c r="AV37" s="3">
-        <v>92.74024963378906</v>
+        <v>92.74025</v>
       </c>
       <c r="AW37" s="3">
-        <v>14.26002979278564</v>
+        <v>14.26003</v>
       </c>
       <c r="AX37" s="3">
         <v>424.5890000000003</v>
@@ -9759,13 +9759,13 @@
         </is>
       </c>
       <c r="AA38" s="3">
-        <v>39.80840301513672</v>
+        <v>39.808403</v>
       </c>
       <c r="AB38" s="3">
-        <v>30.52964782714844</v>
+        <v>30.529648</v>
       </c>
       <c r="AC38" s="3">
-        <v>40.13345718383789</v>
+        <v>40.133457</v>
       </c>
       <c r="AD38" s="3">
         <v>0</v>
@@ -9777,55 +9777,55 @@
         <v>0</v>
       </c>
       <c r="AG38" s="3">
-        <v>0.09138067811727524</v>
+        <v>0.09138068000000001</v>
       </c>
       <c r="AH38" s="3">
-        <v>0.3232181668281555</v>
+        <v>0.32321817</v>
       </c>
       <c r="AI38" s="3">
-        <v>0.7983104586601257</v>
+        <v>0.7983104600000001</v>
       </c>
       <c r="AJ38" s="3">
-        <v>0.07018513232469559</v>
+        <v>0.07018513</v>
       </c>
       <c r="AK38" s="3">
-        <v>0.828957200050354</v>
+        <v>0.8289571999999999</v>
       </c>
       <c r="AL38" s="3">
-        <v>0.03100551292300224</v>
+        <v>0.031005513</v>
       </c>
       <c r="AM38" s="3">
-        <v>0.3484461605548859</v>
+        <v>0.34844616</v>
       </c>
       <c r="AN38" s="3">
-        <v>0.6187785863876343</v>
+        <v>0.6187786</v>
       </c>
       <c r="AO38" s="3">
-        <v>0.1052992343902588</v>
+        <v>0.105299234</v>
       </c>
       <c r="AP38" s="3">
-        <v>0.9706583023071289</v>
+        <v>0.9706583</v>
       </c>
       <c r="AQ38" s="3">
-        <v>0.9993332028388977</v>
+        <v>0.9993332</v>
       </c>
       <c r="AR38" s="3">
-        <v>0.7380698919296265</v>
+        <v>0.7380698999999999</v>
       </c>
       <c r="AS38" s="3">
-        <v>0.8665213584899902</v>
+        <v>0.86652136</v>
       </c>
       <c r="AT38" s="3">
-        <v>0.8680822253227234</v>
+        <v>0.8680822</v>
       </c>
       <c r="AU38" s="3">
-        <v>-5.13906717300415</v>
+        <v>-5.139067</v>
       </c>
       <c r="AV38" s="3">
-        <v>96.92577362060547</v>
+        <v>96.92577</v>
       </c>
       <c r="AW38" s="3">
-        <v>10.45760631561279</v>
+        <v>10.457606</v>
       </c>
       <c r="AX38" s="3">
         <v>502.6590000000003</v>
@@ -9896,7 +9896,7 @@
         <v>1.10712355329196</v>
       </c>
       <c r="M39" s="3">
-        <v>0.3342728036788679</v>
+        <v>0.3342728036788678</v>
       </c>
       <c r="N39" s="3">
         <v>17.07057694297372</v>
@@ -9908,7 +9908,7 @@
         <v>4.892876446708041</v>
       </c>
       <c r="Q39" s="3">
-        <v>0.3342728036788679</v>
+        <v>0.3342728036788678</v>
       </c>
       <c r="R39" s="3">
         <v>2.831058594617665</v>
@@ -9923,7 +9923,7 @@
         <v>5.548051141918621</v>
       </c>
       <c r="V39" s="3">
-        <v>0.3342728036788679</v>
+        <v>0.3342728036788678</v>
       </c>
       <c r="W39" s="3">
         <v>3.265400000000001</v>
@@ -9940,13 +9940,13 @@
         </is>
       </c>
       <c r="AA39" s="3">
-        <v>36.60474014282227</v>
+        <v>36.60474</v>
       </c>
       <c r="AB39" s="3">
-        <v>26.71722984313965</v>
+        <v>26.71723</v>
       </c>
       <c r="AC39" s="3">
-        <v>41.26654815673828</v>
+        <v>41.26655</v>
       </c>
       <c r="AD39" s="3">
         <v>0</v>
@@ -9958,55 +9958,55 @@
         <v>0</v>
       </c>
       <c r="AG39" s="3">
-        <v>0.07388119399547577</v>
+        <v>0.073881194</v>
       </c>
       <c r="AH39" s="3">
-        <v>0.5302248001098633</v>
+        <v>0.5302248000000001</v>
       </c>
       <c r="AI39" s="3">
-        <v>0.7923337817192078</v>
+        <v>0.7923338</v>
       </c>
       <c r="AJ39" s="3">
-        <v>0.1401275098323822</v>
+        <v>0.14012751</v>
       </c>
       <c r="AK39" s="3">
-        <v>0.9181226491928101</v>
+        <v>0.91812265</v>
       </c>
       <c r="AL39" s="3">
-        <v>0.2596137821674347</v>
+        <v>0.25961378</v>
       </c>
       <c r="AM39" s="3">
-        <v>0.5474200248718262</v>
+        <v>0.54742</v>
       </c>
       <c r="AN39" s="3">
-        <v>0.76982182264328</v>
+        <v>0.7698218</v>
       </c>
       <c r="AO39" s="3">
-        <v>0.3111298382282257</v>
+        <v>0.31112984</v>
       </c>
       <c r="AP39" s="3">
-        <v>0.9724744558334351</v>
+        <v>0.97247446</v>
       </c>
       <c r="AQ39" s="3">
-        <v>0.9998326301574707</v>
+        <v>0.99983263</v>
       </c>
       <c r="AR39" s="3">
-        <v>0.7820789813995361</v>
+        <v>0.782079</v>
       </c>
       <c r="AS39" s="3">
-        <v>0.9222691655158997</v>
+        <v>0.92226917</v>
       </c>
       <c r="AT39" s="3">
-        <v>0.8429044485092163</v>
+        <v>0.84290445</v>
       </c>
       <c r="AU39" s="3">
-        <v>-5.332352638244629</v>
+        <v>-5.3323526</v>
       </c>
       <c r="AV39" s="3">
-        <v>94.42604827880859</v>
+        <v>94.42605</v>
       </c>
       <c r="AW39" s="3">
-        <v>11.59303569793701</v>
+        <v>11.593036</v>
       </c>
       <c r="AX39" s="3">
         <v>446.5990000000002</v>
@@ -10077,10 +10077,10 @@
         <v>1.13926712262069</v>
       </c>
       <c r="M40" s="3">
-        <v>0.3398993105004051</v>
+        <v>0.339899310500405</v>
       </c>
       <c r="N40" s="3">
-        <v>18.40683518681118</v>
+        <v>18.40683518681117</v>
       </c>
       <c r="O40" s="3">
         <v>12.97491466301855</v>
@@ -10089,7 +10089,7 @@
         <v>4.860732877379309</v>
       </c>
       <c r="Q40" s="3">
-        <v>0.3398993105004051</v>
+        <v>0.339899310500405</v>
       </c>
       <c r="R40" s="3">
         <v>2.972107229001188</v>
@@ -10104,7 +10104,7 @@
         <v>5.526935525960104</v>
       </c>
       <c r="V40" s="3">
-        <v>0.3398993105004051</v>
+        <v>0.339899310500405</v>
       </c>
       <c r="W40" s="3">
         <v>3.253220000000002</v>
@@ -10121,13 +10121,13 @@
         </is>
       </c>
       <c r="AA40" s="3">
-        <v>55.87805938720703</v>
+        <v>55.87806</v>
       </c>
       <c r="AB40" s="3">
-        <v>47.32645416259766</v>
+        <v>47.326454</v>
       </c>
       <c r="AC40" s="3">
-        <v>40.6223258972168</v>
+        <v>40.622326</v>
       </c>
       <c r="AD40" s="3">
         <v>0</v>
@@ -10139,55 +10139,55 @@
         <v>0</v>
       </c>
       <c r="AG40" s="3">
-        <v>0.1447428315877914</v>
+        <v>0.14474283</v>
       </c>
       <c r="AH40" s="3">
-        <v>0.2311319410800934</v>
+        <v>0.23113194</v>
       </c>
       <c r="AI40" s="3">
-        <v>0.8213003277778625</v>
+        <v>0.8213003</v>
       </c>
       <c r="AJ40" s="3">
-        <v>0.06799375265836716</v>
+        <v>0.06799375000000001</v>
       </c>
       <c r="AK40" s="3">
-        <v>0.8357876539230347</v>
+        <v>0.83578765</v>
       </c>
       <c r="AL40" s="3">
-        <v>0.04919829219579697</v>
+        <v>0.049198292</v>
       </c>
       <c r="AM40" s="3">
-        <v>0.5955426096916199</v>
+        <v>0.5955426</v>
       </c>
       <c r="AN40" s="3">
-        <v>0.7140798568725586</v>
+        <v>0.71407986</v>
       </c>
       <c r="AO40" s="3">
-        <v>0.09219005703926086</v>
+        <v>0.09219006</v>
       </c>
       <c r="AP40" s="3">
-        <v>0.9753450155258179</v>
+        <v>0.975345</v>
       </c>
       <c r="AQ40" s="3">
-        <v>0.9998712539672852</v>
+        <v>0.99987125</v>
       </c>
       <c r="AR40" s="3">
-        <v>0.7210515737533569</v>
+        <v>0.7210516</v>
       </c>
       <c r="AS40" s="3">
-        <v>0.949442982673645</v>
+        <v>0.949443</v>
       </c>
       <c r="AT40" s="3">
-        <v>0.8902240991592407</v>
+        <v>0.8902241</v>
       </c>
       <c r="AU40" s="3">
-        <v>-4.92496395111084</v>
+        <v>-4.924964</v>
       </c>
       <c r="AV40" s="3">
-        <v>98.91422271728516</v>
+        <v>98.91422</v>
       </c>
       <c r="AW40" s="3">
-        <v>11.40245819091797</v>
+        <v>11.402458</v>
       </c>
       <c r="AX40" s="3">
         <v>449.5990000000003</v>
@@ -10302,13 +10302,13 @@
         </is>
       </c>
       <c r="AA41" s="3">
-        <v>55.52654266357422</v>
+        <v>55.526543</v>
       </c>
       <c r="AB41" s="3">
-        <v>50.68181610107422</v>
+        <v>50.681816</v>
       </c>
       <c r="AC41" s="3">
-        <v>41.47741317749023</v>
+        <v>41.477413</v>
       </c>
       <c r="AD41" s="3">
         <v>0</v>
@@ -10320,55 +10320,55 @@
         <v>0</v>
       </c>
       <c r="AG41" s="3">
-        <v>0.1574581563472748</v>
+        <v>0.15745816</v>
       </c>
       <c r="AH41" s="3">
-        <v>0.2561253905296326</v>
+        <v>0.2561254</v>
       </c>
       <c r="AI41" s="3">
-        <v>0.8201186060905457</v>
+        <v>0.8201186</v>
       </c>
       <c r="AJ41" s="3">
-        <v>0.08592627197504044</v>
+        <v>0.08592627</v>
       </c>
       <c r="AK41" s="3">
-        <v>0.8096516728401184</v>
+        <v>0.8096517</v>
       </c>
       <c r="AL41" s="3">
-        <v>0.04234945774078369</v>
+        <v>0.042349458</v>
       </c>
       <c r="AM41" s="3">
-        <v>0.4617823660373688</v>
+        <v>0.46178237</v>
       </c>
       <c r="AN41" s="3">
-        <v>0.6019200682640076</v>
+        <v>0.60192007</v>
       </c>
       <c r="AO41" s="3">
-        <v>0.08626318722963333</v>
+        <v>0.08626319</v>
       </c>
       <c r="AP41" s="3">
-        <v>0.9469621777534485</v>
+        <v>0.9469622</v>
       </c>
       <c r="AQ41" s="3">
-        <v>0.9996334314346313</v>
+        <v>0.99963343</v>
       </c>
       <c r="AR41" s="3">
-        <v>0.7527369856834412</v>
+        <v>0.752737</v>
       </c>
       <c r="AS41" s="3">
-        <v>0.9257534146308899</v>
+        <v>0.9257533999999999</v>
       </c>
       <c r="AT41" s="3">
-        <v>0.8376056551933289</v>
+        <v>0.83760566</v>
       </c>
       <c r="AU41" s="3">
-        <v>-4.933896064758301</v>
+        <v>-4.933896</v>
       </c>
       <c r="AV41" s="3">
-        <v>98.49797058105469</v>
+        <v>98.49797</v>
       </c>
       <c r="AW41" s="3">
-        <v>12.11995410919189</v>
+        <v>12.119954</v>
       </c>
       <c r="AX41" s="3">
         <v>449.5990000000003</v>
@@ -10383,7 +10383,7 @@
         <v>4</v>
       </c>
       <c r="BB41" s="3">
-        <v>3.514032332356759</v>
+        <v>3.51403233235676</v>
       </c>
       <c r="BC41" s="3">
         <v>0.7206630741825824</v>
@@ -10483,13 +10483,13 @@
         </is>
       </c>
       <c r="AA42" s="3">
-        <v>39.99532318115234</v>
+        <v>39.995323</v>
       </c>
       <c r="AB42" s="3">
-        <v>17.48825073242188</v>
+        <v>17.48825</v>
       </c>
       <c r="AC42" s="3">
-        <v>40.00202560424805</v>
+        <v>40.002026</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -10501,55 +10501,55 @@
         <v>0</v>
       </c>
       <c r="AG42" s="3">
-        <v>0.3008598387241364</v>
+        <v>0.30085984</v>
       </c>
       <c r="AH42" s="3">
-        <v>0.3324548900127411</v>
+        <v>0.3324549</v>
       </c>
       <c r="AI42" s="3">
-        <v>0.6367071866989136</v>
+        <v>0.6367072</v>
       </c>
       <c r="AJ42" s="3">
-        <v>0.05809951946139336</v>
+        <v>0.05809952</v>
       </c>
       <c r="AK42" s="3">
-        <v>0.8662105798721313</v>
+        <v>0.8662106000000001</v>
       </c>
       <c r="AL42" s="3">
-        <v>0.1042027324438095</v>
+        <v>0.10420273</v>
       </c>
       <c r="AM42" s="3">
-        <v>0.4313688278198242</v>
+        <v>0.43136883</v>
       </c>
       <c r="AN42" s="3">
-        <v>0.4848213195800781</v>
+        <v>0.48482132</v>
       </c>
       <c r="AO42" s="3">
-        <v>0.1160590797662735</v>
+        <v>0.11605908</v>
       </c>
       <c r="AP42" s="3">
-        <v>0.9708049893379211</v>
+        <v>0.970805</v>
       </c>
       <c r="AQ42" s="3">
-        <v>0.9997732043266296</v>
+        <v>0.9997732</v>
       </c>
       <c r="AR42" s="3">
-        <v>0.7183600664138794</v>
+        <v>0.71836007</v>
       </c>
       <c r="AS42" s="3">
-        <v>0.9332886934280396</v>
+        <v>0.9332887</v>
       </c>
       <c r="AT42" s="3">
-        <v>0.7436832189559937</v>
+        <v>0.7436832</v>
       </c>
       <c r="AU42" s="3">
-        <v>-4.895843029022217</v>
+        <v>-4.895843</v>
       </c>
       <c r="AV42" s="3">
-        <v>96.73207092285156</v>
+        <v>96.73206999999999</v>
       </c>
       <c r="AW42" s="3">
-        <v>10.01155853271484</v>
+        <v>10.011559</v>
       </c>
       <c r="AX42" s="3">
         <v>430.5430000000002</v>
@@ -10641,7 +10641,7 @@
         <v>231.7455231572262</v>
       </c>
       <c r="T43" s="3">
-        <v>3.634988646770919</v>
+        <v>3.63498864677092</v>
       </c>
       <c r="U43" s="3">
         <v>5.716301780562342</v>
@@ -10664,13 +10664,13 @@
         </is>
       </c>
       <c r="AA43" s="3">
-        <v>48.47676467895508</v>
+        <v>48.476765</v>
       </c>
       <c r="AB43" s="3">
-        <v>38.86996459960938</v>
+        <v>38.869965</v>
       </c>
       <c r="AC43" s="3">
-        <v>44.46318817138672</v>
+        <v>44.46319</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -10682,55 +10682,55 @@
         <v>0</v>
       </c>
       <c r="AG43" s="3">
-        <v>0.1436435878276825</v>
+        <v>0.14364359</v>
       </c>
       <c r="AH43" s="3">
-        <v>0.5584583282470703</v>
+        <v>0.5584583</v>
       </c>
       <c r="AI43" s="3">
-        <v>0.7843588590621948</v>
+        <v>0.78435886</v>
       </c>
       <c r="AJ43" s="3">
-        <v>0.1840020716190338</v>
+        <v>0.18400207</v>
       </c>
       <c r="AK43" s="3">
-        <v>0.8965299725532532</v>
+        <v>0.89653</v>
       </c>
       <c r="AL43" s="3">
-        <v>0.3499415814876556</v>
+        <v>0.34994158</v>
       </c>
       <c r="AM43" s="3">
-        <v>0.465552419424057</v>
+        <v>0.46555242</v>
       </c>
       <c r="AN43" s="3">
-        <v>0.6703549027442932</v>
+        <v>0.6703549</v>
       </c>
       <c r="AO43" s="3">
-        <v>0.2939227223396301</v>
+        <v>0.29392272</v>
       </c>
       <c r="AP43" s="3">
-        <v>0.9276121854782104</v>
+        <v>0.9276122</v>
       </c>
       <c r="AQ43" s="3">
-        <v>0.9997462034225464</v>
+        <v>0.9997462</v>
       </c>
       <c r="AR43" s="3">
-        <v>0.8146101236343384</v>
+        <v>0.8146101</v>
       </c>
       <c r="AS43" s="3">
-        <v>0.9354484677314758</v>
+        <v>0.93544847</v>
       </c>
       <c r="AT43" s="3">
-        <v>0.8128904104232788</v>
+        <v>0.8128904</v>
       </c>
       <c r="AU43" s="3">
-        <v>-5.046814441680908</v>
+        <v>-5.0468144</v>
       </c>
       <c r="AV43" s="3">
-        <v>98.88731384277344</v>
+        <v>98.887314</v>
       </c>
       <c r="AW43" s="3">
-        <v>10.91208362579346</v>
+        <v>10.912084</v>
       </c>
       <c r="AX43" s="3">
         <v>435.5720000000002</v>
@@ -10845,13 +10845,13 @@
         </is>
       </c>
       <c r="AA44" s="3">
-        <v>26.28689956665039</v>
+        <v>26.2869</v>
       </c>
       <c r="AB44" s="3">
-        <v>16.91087913513184</v>
+        <v>16.91088</v>
       </c>
       <c r="AC44" s="3">
-        <v>41.00522613525391</v>
+        <v>41.005226</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
@@ -10863,55 +10863,55 @@
         <v>0</v>
       </c>
       <c r="AG44" s="3">
-        <v>0.1082166880369186</v>
+        <v>0.10821669</v>
       </c>
       <c r="AH44" s="3">
-        <v>0.527233898639679</v>
+        <v>0.5272339</v>
       </c>
       <c r="AI44" s="3">
-        <v>0.6385287046432495</v>
+        <v>0.6385286999999999</v>
       </c>
       <c r="AJ44" s="3">
-        <v>0.1533090770244598</v>
+        <v>0.15330908</v>
       </c>
       <c r="AK44" s="3">
-        <v>0.9715156555175781</v>
+        <v>0.97151566</v>
       </c>
       <c r="AL44" s="3">
-        <v>0.2450113594532013</v>
+        <v>0.24501136</v>
       </c>
       <c r="AM44" s="3">
-        <v>0.4739505350589752</v>
+        <v>0.47395054</v>
       </c>
       <c r="AN44" s="3">
-        <v>0.6461736559867859</v>
+        <v>0.64617366</v>
       </c>
       <c r="AO44" s="3">
-        <v>0.5807135701179504</v>
+        <v>0.58071357</v>
       </c>
       <c r="AP44" s="3">
-        <v>0.9790089726448059</v>
+        <v>0.979009</v>
       </c>
       <c r="AQ44" s="3">
-        <v>0.9993442296981812</v>
+        <v>0.9993442</v>
       </c>
       <c r="AR44" s="3">
-        <v>0.6593407988548279</v>
+        <v>0.6593407999999999</v>
       </c>
       <c r="AS44" s="3">
-        <v>0.8649691343307495</v>
+        <v>0.86496913</v>
       </c>
       <c r="AT44" s="3">
-        <v>0.8415617942810059</v>
+        <v>0.8415618</v>
       </c>
       <c r="AU44" s="3">
-        <v>-5.504205703735352</v>
+        <v>-5.5042057</v>
       </c>
       <c r="AV44" s="3">
-        <v>89.31491088867188</v>
+        <v>89.31491</v>
       </c>
       <c r="AW44" s="3">
-        <v>14.42622089385986</v>
+        <v>14.426221</v>
       </c>
       <c r="AX44" s="3">
         <v>474.6530000000003</v>
@@ -10920,7 +10920,7 @@
         <v>3.199300000000001</v>
       </c>
       <c r="AZ44" s="3">
-        <v>0.406226497214062</v>
+        <v>0.4062264972140619</v>
       </c>
       <c r="BA44" s="3">
         <v>4</v>
@@ -10997,7 +10997,7 @@
         <v>0.5417137745929465</v>
       </c>
       <c r="R45" s="3">
-        <v>1.897263716495194</v>
+        <v>1.897263716495193</v>
       </c>
       <c r="S45" s="3">
         <v>252.1422928127023</v>
@@ -11026,13 +11026,13 @@
         </is>
       </c>
       <c r="AA45" s="3">
-        <v>26.91288375854492</v>
+        <v>26.912884</v>
       </c>
       <c r="AB45" s="3">
-        <v>17.39401435852051</v>
+        <v>17.394014</v>
       </c>
       <c r="AC45" s="3">
-        <v>48.46894073486328</v>
+        <v>48.46894</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
@@ -11044,55 +11044,55 @@
         <v>0</v>
       </c>
       <c r="AG45" s="3">
-        <v>0.07611661404371262</v>
+        <v>0.076116614</v>
       </c>
       <c r="AH45" s="3">
-        <v>0.4940494894981384</v>
+        <v>0.4940495</v>
       </c>
       <c r="AI45" s="3">
-        <v>0.5864124894142151</v>
+        <v>0.5864125</v>
       </c>
       <c r="AJ45" s="3">
-        <v>0.1302315890789032</v>
+        <v>0.13023159</v>
       </c>
       <c r="AK45" s="3">
-        <v>0.9694560170173645</v>
+        <v>0.969456</v>
       </c>
       <c r="AL45" s="3">
-        <v>0.1759836375713348</v>
+        <v>0.17598364</v>
       </c>
       <c r="AM45" s="3">
-        <v>0.3355216383934021</v>
+        <v>0.33552164</v>
       </c>
       <c r="AN45" s="3">
-        <v>0.4819319844245911</v>
+        <v>0.48193198</v>
       </c>
       <c r="AO45" s="3">
-        <v>0.4918285012245178</v>
+        <v>0.4918285</v>
       </c>
       <c r="AP45" s="3">
-        <v>0.9687244296073914</v>
+        <v>0.9687244</v>
       </c>
       <c r="AQ45" s="3">
-        <v>0.9994006156921387</v>
+        <v>0.9994006</v>
       </c>
       <c r="AR45" s="3">
-        <v>0.7337114214897156</v>
+        <v>0.7337114</v>
       </c>
       <c r="AS45" s="3">
-        <v>0.8752544522285461</v>
+        <v>0.87525445</v>
       </c>
       <c r="AT45" s="3">
-        <v>0.7717357873916626</v>
+        <v>0.7717358</v>
       </c>
       <c r="AU45" s="3">
-        <v>-5.479255676269531</v>
+        <v>-5.4792557</v>
       </c>
       <c r="AV45" s="3">
-        <v>85.95934295654297</v>
+        <v>85.95934</v>
       </c>
       <c r="AW45" s="3">
-        <v>16.88933563232422</v>
+        <v>16.889336</v>
       </c>
       <c r="AX45" s="3">
         <v>488.6800000000003</v>
@@ -11101,7 +11101,7 @@
         <v>3.460000000000002</v>
       </c>
       <c r="AZ45" s="3">
-        <v>0.372847715364346</v>
+        <v>0.3728477153643459</v>
       </c>
       <c r="BA45" s="3">
         <v>4</v>
@@ -11178,7 +11178,7 @@
         <v>0.5438799897602478</v>
       </c>
       <c r="R46" s="3">
-        <v>1.709483188949833</v>
+        <v>1.709483188949832</v>
       </c>
       <c r="S46" s="3">
         <v>231.6724514342681</v>
@@ -11207,13 +11207,13 @@
         </is>
       </c>
       <c r="AA46" s="3">
-        <v>25.42239379882812</v>
+        <v>25.422394</v>
       </c>
       <c r="AB46" s="3">
-        <v>10.9663667678833</v>
+        <v>10.966367</v>
       </c>
       <c r="AC46" s="3">
-        <v>49.29924392700195</v>
+        <v>49.299244</v>
       </c>
       <c r="AD46" s="3">
         <v>0</v>
@@ -11225,55 +11225,55 @@
         <v>0</v>
       </c>
       <c r="AG46" s="3">
-        <v>0.1347719132900238</v>
+        <v>0.13477191</v>
       </c>
       <c r="AH46" s="3">
-        <v>0.4488030076026917</v>
+        <v>0.448803</v>
       </c>
       <c r="AI46" s="3">
-        <v>0.5508708953857422</v>
+        <v>0.5508709000000001</v>
       </c>
       <c r="AJ46" s="3">
-        <v>0.1450610905885696</v>
+        <v>0.14506109</v>
       </c>
       <c r="AK46" s="3">
-        <v>0.9710986018180847</v>
+        <v>0.9710986</v>
       </c>
       <c r="AL46" s="3">
-        <v>0.23394575715065</v>
+        <v>0.23394576</v>
       </c>
       <c r="AM46" s="3">
-        <v>0.5000661611557007</v>
+        <v>0.50006616</v>
       </c>
       <c r="AN46" s="3">
-        <v>0.6328191757202148</v>
+        <v>0.6328192</v>
       </c>
       <c r="AO46" s="3">
-        <v>0.6060531735420227</v>
+        <v>0.6060532</v>
       </c>
       <c r="AP46" s="3">
-        <v>0.9737003445625305</v>
+        <v>0.9737003400000001</v>
       </c>
       <c r="AQ46" s="3">
-        <v>0.9983922243118286</v>
+        <v>0.9983922</v>
       </c>
       <c r="AR46" s="3">
-        <v>0.5791388750076294</v>
+        <v>0.5791389</v>
       </c>
       <c r="AS46" s="3">
-        <v>0.8365917205810547</v>
+        <v>0.8365917</v>
       </c>
       <c r="AT46" s="3">
-        <v>0.8486098051071167</v>
+        <v>0.8486098</v>
       </c>
       <c r="AU46" s="3">
-        <v>-5.585998058319092</v>
+        <v>-5.585998</v>
       </c>
       <c r="AV46" s="3">
-        <v>90.25538635253906</v>
+        <v>90.25539000000001</v>
       </c>
       <c r="AW46" s="3">
-        <v>16.35267448425293</v>
+        <v>16.352674</v>
       </c>
       <c r="AX46" s="3">
         <v>462.6420000000003</v>
@@ -11388,13 +11388,13 @@
         </is>
       </c>
       <c r="AA47" s="3">
-        <v>55.1284065246582</v>
+        <v>55.128407</v>
       </c>
       <c r="AB47" s="3">
-        <v>50.74510955810547</v>
+        <v>50.74511</v>
       </c>
       <c r="AC47" s="3">
-        <v>49.07013320922852</v>
+        <v>49.070133</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
@@ -11406,55 +11406,55 @@
         <v>0</v>
       </c>
       <c r="AG47" s="3">
-        <v>0.1133022531867027</v>
+        <v>0.11330225</v>
       </c>
       <c r="AH47" s="3">
-        <v>0.2449150830507278</v>
+        <v>0.24491508</v>
       </c>
       <c r="AI47" s="3">
-        <v>0.8536427617073059</v>
+        <v>0.8536427599999999</v>
       </c>
       <c r="AJ47" s="3">
-        <v>0.07795068621635437</v>
+        <v>0.07795068600000001</v>
       </c>
       <c r="AK47" s="3">
-        <v>0.7956396341323853</v>
+        <v>0.79563963</v>
       </c>
       <c r="AL47" s="3">
-        <v>0.280020147562027</v>
+        <v>0.28002015</v>
       </c>
       <c r="AM47" s="3">
-        <v>0.6198892593383789</v>
+        <v>0.61988926</v>
       </c>
       <c r="AN47" s="3">
-        <v>0.8413428068161011</v>
+        <v>0.8413427999999999</v>
       </c>
       <c r="AO47" s="3">
-        <v>0.124850369989872</v>
+        <v>0.12485037</v>
       </c>
       <c r="AP47" s="3">
-        <v>0.9690201878547668</v>
+        <v>0.9690202</v>
       </c>
       <c r="AQ47" s="3">
-        <v>0.9999104738235474</v>
+        <v>0.9999105</v>
       </c>
       <c r="AR47" s="3">
-        <v>0.7288022041320801</v>
+        <v>0.7288022</v>
       </c>
       <c r="AS47" s="3">
-        <v>0.9518684148788452</v>
+        <v>0.9518683999999999</v>
       </c>
       <c r="AT47" s="3">
-        <v>0.8861129879951477</v>
+        <v>0.886113</v>
       </c>
       <c r="AU47" s="3">
-        <v>-4.771246433258057</v>
+        <v>-4.7712464</v>
       </c>
       <c r="AV47" s="3">
-        <v>100.8254928588867</v>
+        <v>100.82549</v>
       </c>
       <c r="AW47" s="3">
-        <v>9.469991683959961</v>
+        <v>9.469992</v>
       </c>
       <c r="AX47" s="3">
         <v>418.5410000000002</v>
@@ -11569,13 +11569,13 @@
         </is>
       </c>
       <c r="AA48" s="3">
-        <v>41.02350997924805</v>
+        <v>41.02351</v>
       </c>
       <c r="AB48" s="3">
-        <v>32.05742645263672</v>
+        <v>32.057426</v>
       </c>
       <c r="AC48" s="3">
-        <v>42.91416549682617</v>
+        <v>42.914165</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -11587,55 +11587,55 @@
         <v>0</v>
       </c>
       <c r="AG48" s="3">
-        <v>0.1897450834512711</v>
+        <v>0.18974508</v>
       </c>
       <c r="AH48" s="3">
-        <v>0.5659934282302856</v>
+        <v>0.5659934</v>
       </c>
       <c r="AI48" s="3">
-        <v>0.7691575288772583</v>
+        <v>0.7691575</v>
       </c>
       <c r="AJ48" s="3">
-        <v>0.166671097278595</v>
+        <v>0.1666711</v>
       </c>
       <c r="AK48" s="3">
-        <v>0.9312096834182739</v>
+        <v>0.9312097</v>
       </c>
       <c r="AL48" s="3">
-        <v>0.4071165025234222</v>
+        <v>0.4071165</v>
       </c>
       <c r="AM48" s="3">
-        <v>0.6137876510620117</v>
+        <v>0.61378765</v>
       </c>
       <c r="AN48" s="3">
-        <v>0.7541599273681641</v>
+        <v>0.7541599</v>
       </c>
       <c r="AO48" s="3">
-        <v>0.3692933320999146</v>
+        <v>0.36929333</v>
       </c>
       <c r="AP48" s="3">
-        <v>0.9614629745483398</v>
+        <v>0.961463</v>
       </c>
       <c r="AQ48" s="3">
-        <v>0.9998534321784973</v>
+        <v>0.99985343</v>
       </c>
       <c r="AR48" s="3">
-        <v>0.7693444490432739</v>
+        <v>0.76934445</v>
       </c>
       <c r="AS48" s="3">
-        <v>0.944850742816925</v>
+        <v>0.94485074</v>
       </c>
       <c r="AT48" s="3">
-        <v>0.8567095994949341</v>
+        <v>0.8567096</v>
       </c>
       <c r="AU48" s="3">
-        <v>-5.091917514801025</v>
+        <v>-5.0919175</v>
       </c>
       <c r="AV48" s="3">
-        <v>98.28615570068359</v>
+        <v>98.28615600000001</v>
       </c>
       <c r="AW48" s="3">
-        <v>11.00429725646973</v>
+        <v>11.004297</v>
       </c>
       <c r="AX48" s="3">
         <v>435.5720000000002</v>
@@ -11750,13 +11750,13 @@
         </is>
       </c>
       <c r="AA49" s="3">
-        <v>39.26168441772461</v>
+        <v>39.261684</v>
       </c>
       <c r="AB49" s="3">
-        <v>26.26993370056152</v>
+        <v>26.269934</v>
       </c>
       <c r="AC49" s="3">
-        <v>48.15713882446289</v>
+        <v>48.15714</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -11768,55 +11768,55 @@
         <v>0</v>
       </c>
       <c r="AG49" s="3">
-        <v>0.07308562099933624</v>
+        <v>0.07308562</v>
       </c>
       <c r="AH49" s="3">
-        <v>0.485703706741333</v>
+        <v>0.4857037</v>
       </c>
       <c r="AI49" s="3">
-        <v>0.7603539824485779</v>
+        <v>0.760354</v>
       </c>
       <c r="AJ49" s="3">
-        <v>0.1691804230213165</v>
+        <v>0.16918042</v>
       </c>
       <c r="AK49" s="3">
-        <v>0.8909358978271484</v>
+        <v>0.8909359</v>
       </c>
       <c r="AL49" s="3">
-        <v>0.3086290955543518</v>
+        <v>0.3086291</v>
       </c>
       <c r="AM49" s="3">
-        <v>0.4890358448028564</v>
+        <v>0.48903584</v>
       </c>
       <c r="AN49" s="3">
-        <v>0.6964751482009888</v>
+        <v>0.69647515</v>
       </c>
       <c r="AO49" s="3">
-        <v>0.3070812225341797</v>
+        <v>0.30708122</v>
       </c>
       <c r="AP49" s="3">
-        <v>0.9330641031265259</v>
+        <v>0.9330641</v>
       </c>
       <c r="AQ49" s="3">
-        <v>0.999228835105896</v>
+        <v>0.99922884</v>
       </c>
       <c r="AR49" s="3">
-        <v>0.8018847703933716</v>
+        <v>0.8018848</v>
       </c>
       <c r="AS49" s="3">
-        <v>0.8875892758369446</v>
+        <v>0.8875893</v>
       </c>
       <c r="AT49" s="3">
-        <v>0.7157986760139465</v>
+        <v>0.7157987</v>
       </c>
       <c r="AU49" s="3">
-        <v>-5.32430362701416</v>
+        <v>-5.3243036</v>
       </c>
       <c r="AV49" s="3">
-        <v>98.07049560546875</v>
+        <v>98.07049600000001</v>
       </c>
       <c r="AW49" s="3">
-        <v>12.34997749328613</v>
+        <v>12.3499775</v>
       </c>
       <c r="AX49" s="3">
         <v>434.5880000000002</v>
@@ -11931,13 +11931,13 @@
         </is>
       </c>
       <c r="AA50" s="3">
-        <v>39.80806732177734</v>
+        <v>39.808067</v>
       </c>
       <c r="AB50" s="3">
-        <v>22.27601432800293</v>
+        <v>22.276014</v>
       </c>
       <c r="AC50" s="3">
-        <v>49.35817337036133</v>
+        <v>49.358173</v>
       </c>
       <c r="AD50" s="3">
         <v>0</v>
@@ -11949,55 +11949,55 @@
         <v>0</v>
       </c>
       <c r="AG50" s="3">
-        <v>0.1109714731574059</v>
+        <v>0.11097147</v>
       </c>
       <c r="AH50" s="3">
-        <v>0.4736871719360352</v>
+        <v>0.47368717</v>
       </c>
       <c r="AI50" s="3">
-        <v>0.7462054491043091</v>
+        <v>0.74620545</v>
       </c>
       <c r="AJ50" s="3">
-        <v>0.1770730316638947</v>
+        <v>0.17707303</v>
       </c>
       <c r="AK50" s="3">
-        <v>0.9070793986320496</v>
+        <v>0.9070794</v>
       </c>
       <c r="AL50" s="3">
-        <v>0.3010877966880798</v>
+        <v>0.3010878</v>
       </c>
       <c r="AM50" s="3">
-        <v>0.5116009116172791</v>
+        <v>0.5116009</v>
       </c>
       <c r="AN50" s="3">
-        <v>0.7008902430534363</v>
+        <v>0.70089024</v>
       </c>
       <c r="AO50" s="3">
-        <v>0.3266811966896057</v>
+        <v>0.3266812</v>
       </c>
       <c r="AP50" s="3">
-        <v>0.9490151405334473</v>
+        <v>0.94901514</v>
       </c>
       <c r="AQ50" s="3">
-        <v>0.9991229176521301</v>
+        <v>0.9991229</v>
       </c>
       <c r="AR50" s="3">
-        <v>0.7781740427017212</v>
+        <v>0.77817404</v>
       </c>
       <c r="AS50" s="3">
-        <v>0.8758136034011841</v>
+        <v>0.8758136</v>
       </c>
       <c r="AT50" s="3">
-        <v>0.7202772498130798</v>
+        <v>0.72027725</v>
       </c>
       <c r="AU50" s="3">
-        <v>-5.340922355651855</v>
+        <v>-5.3409224</v>
       </c>
       <c r="AV50" s="3">
-        <v>97.73011016845703</v>
+        <v>97.73011</v>
       </c>
       <c r="AW50" s="3">
-        <v>12.19048500061035</v>
+        <v>12.190485</v>
       </c>
       <c r="AX50" s="3">
         <v>434.5880000000002</v>
@@ -12065,7 +12065,7 @@
         <v>5.302380392493043</v>
       </c>
       <c r="L51" s="3">
-        <v>1.345131472932253</v>
+        <v>1.345131472932252</v>
       </c>
       <c r="M51" s="3">
         <v>0.5530030354105827</v>
@@ -12112,13 +12112,13 @@
         </is>
       </c>
       <c r="AA51" s="3">
-        <v>45.72786331176758</v>
+        <v>45.727863</v>
       </c>
       <c r="AB51" s="3">
-        <v>30.69501304626465</v>
+        <v>30.695013</v>
       </c>
       <c r="AC51" s="3">
-        <v>47.00536727905273</v>
+        <v>47.005367</v>
       </c>
       <c r="AD51" s="3">
         <v>0</v>
@@ -12130,55 +12130,55 @@
         <v>0</v>
       </c>
       <c r="AG51" s="3">
-        <v>0.1561215072870255</v>
+        <v>0.1561215</v>
       </c>
       <c r="AH51" s="3">
-        <v>0.5728350877761841</v>
+        <v>0.5728351</v>
       </c>
       <c r="AI51" s="3">
-        <v>0.7418969869613647</v>
+        <v>0.741897</v>
       </c>
       <c r="AJ51" s="3">
-        <v>0.145254522562027</v>
+        <v>0.14525452</v>
       </c>
       <c r="AK51" s="3">
-        <v>0.9472109079360962</v>
+        <v>0.9472109</v>
       </c>
       <c r="AL51" s="3">
-        <v>0.2527392506599426</v>
+        <v>0.25273925</v>
       </c>
       <c r="AM51" s="3">
-        <v>0.5005385875701904</v>
+        <v>0.5005385999999999</v>
       </c>
       <c r="AN51" s="3">
-        <v>0.6642271280288696</v>
+        <v>0.6642271</v>
       </c>
       <c r="AO51" s="3">
-        <v>0.3539374470710754</v>
+        <v>0.35393745</v>
       </c>
       <c r="AP51" s="3">
-        <v>0.9691165089607239</v>
+        <v>0.9691165</v>
       </c>
       <c r="AQ51" s="3">
-        <v>0.9997466206550598</v>
+        <v>0.9997466</v>
       </c>
       <c r="AR51" s="3">
-        <v>0.774871826171875</v>
+        <v>0.7748718</v>
       </c>
       <c r="AS51" s="3">
-        <v>0.9263246655464172</v>
+        <v>0.92632467</v>
       </c>
       <c r="AT51" s="3">
-        <v>0.8505237698554993</v>
+        <v>0.85052377</v>
       </c>
       <c r="AU51" s="3">
-        <v>-5.192787647247314</v>
+        <v>-5.1927876</v>
       </c>
       <c r="AV51" s="3">
-        <v>97.70104217529297</v>
+        <v>97.70104000000001</v>
       </c>
       <c r="AW51" s="3">
-        <v>12.34895133972168</v>
+        <v>12.348951</v>
       </c>
       <c r="AX51" s="3">
         <v>448.6150000000002</v>
@@ -12282,7 +12282,7 @@
         <v>3.075100000000001</v>
       </c>
       <c r="X52" s="3">
-        <v>-5.023048563370843</v>
+        <v>-5.023048563370844</v>
       </c>
       <c r="Y52" s="3">
         <v>9.483124158505878E-06</v>
@@ -12293,13 +12293,13 @@
         </is>
       </c>
       <c r="AA52" s="3">
-        <v>28.67998695373535</v>
+        <v>28.679987</v>
       </c>
       <c r="AB52" s="3">
-        <v>15.90644836425781</v>
+        <v>15.906448</v>
       </c>
       <c r="AC52" s="3">
-        <v>41.41524124145508</v>
+        <v>41.41524</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
@@ -12311,55 +12311,55 @@
         <v>0</v>
       </c>
       <c r="AG52" s="3">
-        <v>0.2676908075809479</v>
+        <v>0.2676908</v>
       </c>
       <c r="AH52" s="3">
-        <v>0.5950355529785156</v>
+        <v>0.59503555</v>
       </c>
       <c r="AI52" s="3">
-        <v>0.5711034536361694</v>
+        <v>0.57110345</v>
       </c>
       <c r="AJ52" s="3">
-        <v>0.08864458650350571</v>
+        <v>0.08864459</v>
       </c>
       <c r="AK52" s="3">
-        <v>0.9581760168075562</v>
+        <v>0.958176</v>
       </c>
       <c r="AL52" s="3">
-        <v>0.2427808940410614</v>
+        <v>0.2427809</v>
       </c>
       <c r="AM52" s="3">
-        <v>0.3965744972229004</v>
+        <v>0.3965745</v>
       </c>
       <c r="AN52" s="3">
-        <v>0.4812158644199371</v>
+        <v>0.48121586</v>
       </c>
       <c r="AO52" s="3">
-        <v>0.49625563621521</v>
+        <v>0.49625564</v>
       </c>
       <c r="AP52" s="3">
-        <v>0.9700689315795898</v>
+        <v>0.9700689300000001</v>
       </c>
       <c r="AQ52" s="3">
-        <v>0.9995460510253906</v>
+        <v>0.99954605</v>
       </c>
       <c r="AR52" s="3">
-        <v>0.6627799272537231</v>
+        <v>0.6627799</v>
       </c>
       <c r="AS52" s="3">
-        <v>0.8934614062309265</v>
+        <v>0.8934614</v>
       </c>
       <c r="AT52" s="3">
-        <v>0.8273037075996399</v>
+        <v>0.8273037</v>
       </c>
       <c r="AU52" s="3">
-        <v>-5.211467742919922</v>
+        <v>-5.2114677</v>
       </c>
       <c r="AV52" s="3">
-        <v>94.44547271728516</v>
+        <v>94.44547</v>
       </c>
       <c r="AW52" s="3">
-        <v>12.1214485168457</v>
+        <v>12.1214485</v>
       </c>
       <c r="AX52" s="3">
         <v>447.6270000000002</v>
@@ -12445,7 +12445,7 @@
         <v>0.554018124838383</v>
       </c>
       <c r="R53" s="3">
-        <v>1.736316725844338</v>
+        <v>1.736316725844337</v>
       </c>
       <c r="S53" s="3">
         <v>257.8576368122508</v>
@@ -12474,13 +12474,13 @@
         </is>
       </c>
       <c r="AA53" s="3">
-        <v>46.36356353759766</v>
+        <v>46.363564</v>
       </c>
       <c r="AB53" s="3">
-        <v>36.2490234375</v>
+        <v>36.249023</v>
       </c>
       <c r="AC53" s="3">
-        <v>46.93537902832031</v>
+        <v>46.93538</v>
       </c>
       <c r="AD53" s="3">
         <v>0</v>
@@ -12492,55 +12492,55 @@
         <v>0</v>
       </c>
       <c r="AG53" s="3">
-        <v>0.09368102252483368</v>
+        <v>0.09368102</v>
       </c>
       <c r="AH53" s="3">
-        <v>0.2559710443019867</v>
+        <v>0.25597104</v>
       </c>
       <c r="AI53" s="3">
-        <v>0.8333752751350403</v>
+        <v>0.8333753</v>
       </c>
       <c r="AJ53" s="3">
-        <v>0.0713336318731308</v>
+        <v>0.07133363</v>
       </c>
       <c r="AK53" s="3">
-        <v>0.8434513211250305</v>
+        <v>0.8434513</v>
       </c>
       <c r="AL53" s="3">
-        <v>0.5750225782394409</v>
+        <v>0.5750226000000001</v>
       </c>
       <c r="AM53" s="3">
-        <v>0.8080711364746094</v>
+        <v>0.80807114</v>
       </c>
       <c r="AN53" s="3">
-        <v>0.8854955434799194</v>
+        <v>0.88549554</v>
       </c>
       <c r="AO53" s="3">
-        <v>0.1792305260896683</v>
+        <v>0.17923053</v>
       </c>
       <c r="AP53" s="3">
-        <v>0.9843473434448242</v>
+        <v>0.98434734</v>
       </c>
       <c r="AQ53" s="3">
-        <v>0.9999586343765259</v>
+        <v>0.99995863</v>
       </c>
       <c r="AR53" s="3">
-        <v>0.7203251123428345</v>
+        <v>0.7203251000000001</v>
       </c>
       <c r="AS53" s="3">
-        <v>0.9636925458908081</v>
+        <v>0.96369255</v>
       </c>
       <c r="AT53" s="3">
-        <v>0.7818160057067871</v>
+        <v>0.781816</v>
       </c>
       <c r="AU53" s="3">
-        <v>-4.939343452453613</v>
+        <v>-4.9393435</v>
       </c>
       <c r="AV53" s="3">
-        <v>100.4122695922852</v>
+        <v>100.41227</v>
       </c>
       <c r="AW53" s="3">
-        <v>9.496963500976562</v>
+        <v>9.4969635</v>
       </c>
       <c r="AX53" s="3">
         <v>391.5190000000001</v>
@@ -12555,7 +12555,7 @@
         <v>4</v>
       </c>
       <c r="BB53" s="3">
-        <v>3.494383926506519</v>
+        <v>3.494383926506518</v>
       </c>
       <c r="BC53" s="3">
         <v>0.7228462303881646</v>
@@ -12655,13 +12655,13 @@
         </is>
       </c>
       <c r="AA54" s="3">
-        <v>62.83623123168945</v>
+        <v>62.83623</v>
       </c>
       <c r="AB54" s="3">
-        <v>60.1665153503418</v>
+        <v>60.166515</v>
       </c>
       <c r="AC54" s="3">
-        <v>48.18215179443359</v>
+        <v>48.18215</v>
       </c>
       <c r="AD54" s="3">
         <v>0</v>
@@ -12673,55 +12673,55 @@
         <v>0</v>
       </c>
       <c r="AG54" s="3">
-        <v>0.1282973736524582</v>
+        <v>0.12829737</v>
       </c>
       <c r="AH54" s="3">
-        <v>0.2607911825180054</v>
+        <v>0.26079118</v>
       </c>
       <c r="AI54" s="3">
-        <v>0.8436020612716675</v>
+        <v>0.84360206</v>
       </c>
       <c r="AJ54" s="3">
-        <v>0.08913099765777588</v>
+        <v>0.089131</v>
       </c>
       <c r="AK54" s="3">
-        <v>0.8110896944999695</v>
+        <v>0.8110897</v>
       </c>
       <c r="AL54" s="3">
-        <v>0.4075813889503479</v>
+        <v>0.4075814</v>
       </c>
       <c r="AM54" s="3">
-        <v>0.7175242900848389</v>
+        <v>0.7175243</v>
       </c>
       <c r="AN54" s="3">
-        <v>0.8229074478149414</v>
+        <v>0.82290745</v>
       </c>
       <c r="AO54" s="3">
-        <v>0.1541028469800949</v>
+        <v>0.15410285</v>
       </c>
       <c r="AP54" s="3">
-        <v>0.9670270085334778</v>
+        <v>0.967027</v>
       </c>
       <c r="AQ54" s="3">
-        <v>0.999778151512146</v>
+        <v>0.99977815</v>
       </c>
       <c r="AR54" s="3">
-        <v>0.7362948656082153</v>
+        <v>0.73629487</v>
       </c>
       <c r="AS54" s="3">
-        <v>0.9462138414382935</v>
+        <v>0.94621384</v>
       </c>
       <c r="AT54" s="3">
-        <v>0.7763729095458984</v>
+        <v>0.7763729</v>
       </c>
       <c r="AU54" s="3">
-        <v>-4.844556331634521</v>
+        <v>-4.8445563</v>
       </c>
       <c r="AV54" s="3">
-        <v>100.9472427368164</v>
+        <v>100.94724</v>
       </c>
       <c r="AW54" s="3">
-        <v>9.599960327148438</v>
+        <v>9.599959999999999</v>
       </c>
       <c r="AX54" s="3">
         <v>391.5190000000001</v>
@@ -12836,13 +12836,13 @@
         </is>
       </c>
       <c r="AA55" s="3">
-        <v>61.61127853393555</v>
+        <v>61.61128</v>
       </c>
       <c r="AB55" s="3">
-        <v>52.67633056640625</v>
+        <v>52.67633</v>
       </c>
       <c r="AC55" s="3">
-        <v>45.03598785400391</v>
+        <v>45.035988</v>
       </c>
       <c r="AD55" s="3">
         <v>0</v>
@@ -12854,55 +12854,55 @@
         <v>0</v>
       </c>
       <c r="AG55" s="3">
-        <v>0.08297605812549591</v>
+        <v>0.08297606</v>
       </c>
       <c r="AH55" s="3">
-        <v>0.2512148320674896</v>
+        <v>0.25121483</v>
       </c>
       <c r="AI55" s="3">
-        <v>0.9436495900154114</v>
+        <v>0.9436496</v>
       </c>
       <c r="AJ55" s="3">
-        <v>0.1274960935115814</v>
+        <v>0.1274961</v>
       </c>
       <c r="AK55" s="3">
-        <v>0.7050577402114868</v>
+        <v>0.70505774</v>
       </c>
       <c r="AL55" s="3">
-        <v>0.258673369884491</v>
+        <v>0.25867337</v>
       </c>
       <c r="AM55" s="3">
-        <v>0.4184069633483887</v>
+        <v>0.41840696</v>
       </c>
       <c r="AN55" s="3">
-        <v>0.7295550107955933</v>
+        <v>0.729555</v>
       </c>
       <c r="AO55" s="3">
-        <v>0.05188794061541557</v>
+        <v>0.05188794</v>
       </c>
       <c r="AP55" s="3">
-        <v>0.9059159159660339</v>
+        <v>0.9059159</v>
       </c>
       <c r="AQ55" s="3">
-        <v>0.9995496869087219</v>
+        <v>0.9995497</v>
       </c>
       <c r="AR55" s="3">
-        <v>0.8504105806350708</v>
+        <v>0.8504106</v>
       </c>
       <c r="AS55" s="3">
-        <v>0.9412958025932312</v>
+        <v>0.9412958</v>
       </c>
       <c r="AT55" s="3">
-        <v>0.7490119934082031</v>
+        <v>0.749012</v>
       </c>
       <c r="AU55" s="3">
-        <v>-4.757860660552979</v>
+        <v>-4.7578607</v>
       </c>
       <c r="AV55" s="3">
-        <v>101.9753646850586</v>
+        <v>101.975365</v>
       </c>
       <c r="AW55" s="3">
-        <v>6.259325981140137</v>
+        <v>6.259326</v>
       </c>
       <c r="AX55" s="3">
         <v>428.5400000000002</v>
@@ -12988,7 +12988,7 @@
         <v>0.5571052531548235</v>
       </c>
       <c r="R56" s="3">
-        <v>1.834652228682274</v>
+        <v>1.834652228682273</v>
       </c>
       <c r="S56" s="3">
         <v>280.160139613277</v>
@@ -13017,13 +13017,13 @@
         </is>
       </c>
       <c r="AA56" s="3">
-        <v>54.39677810668945</v>
+        <v>54.39678</v>
       </c>
       <c r="AB56" s="3">
-        <v>43.51390838623047</v>
+        <v>43.51391</v>
       </c>
       <c r="AC56" s="3">
-        <v>48.423583984375</v>
+        <v>48.423584</v>
       </c>
       <c r="AD56" s="3">
         <v>0</v>
@@ -13035,55 +13035,55 @@
         <v>0</v>
       </c>
       <c r="AG56" s="3">
-        <v>0.08093960583209991</v>
+        <v>0.080939606</v>
       </c>
       <c r="AH56" s="3">
-        <v>0.3356663286685944</v>
+        <v>0.33566633</v>
       </c>
       <c r="AI56" s="3">
-        <v>0.8311381340026855</v>
+        <v>0.83113813</v>
       </c>
       <c r="AJ56" s="3">
-        <v>0.09820558875799179</v>
+        <v>0.09820559</v>
       </c>
       <c r="AK56" s="3">
-        <v>0.8279390335083008</v>
+        <v>0.82793903</v>
       </c>
       <c r="AL56" s="3">
-        <v>0.3399052321910858</v>
+        <v>0.33990523</v>
       </c>
       <c r="AM56" s="3">
-        <v>0.5811737775802612</v>
+        <v>0.5811738</v>
       </c>
       <c r="AN56" s="3">
-        <v>0.7533446550369263</v>
+        <v>0.75334466</v>
       </c>
       <c r="AO56" s="3">
-        <v>0.1522260159254074</v>
+        <v>0.15222602</v>
       </c>
       <c r="AP56" s="3">
-        <v>0.9433992505073547</v>
+        <v>0.94339925</v>
       </c>
       <c r="AQ56" s="3">
-        <v>0.9997081756591797</v>
+        <v>0.9997082</v>
       </c>
       <c r="AR56" s="3">
-        <v>0.7786367535591125</v>
+        <v>0.77863675</v>
       </c>
       <c r="AS56" s="3">
-        <v>0.9319178462028503</v>
+        <v>0.93191785</v>
       </c>
       <c r="AT56" s="3">
-        <v>0.7318788766860962</v>
+        <v>0.7318789</v>
       </c>
       <c r="AU56" s="3">
-        <v>-4.921243190765381</v>
+        <v>-4.921243</v>
       </c>
       <c r="AV56" s="3">
-        <v>100.7332534790039</v>
+        <v>100.73325</v>
       </c>
       <c r="AW56" s="3">
-        <v>9.648932456970215</v>
+        <v>9.648932</v>
       </c>
       <c r="AX56" s="3">
         <v>391.5190000000001</v>
@@ -13098,7 +13098,7 @@
         <v>4</v>
       </c>
       <c r="BB56" s="3">
-        <v>3.556058651781243</v>
+        <v>3.556058651781244</v>
       </c>
       <c r="BC56" s="3">
         <v>0.7159934831354173</v>
@@ -13198,13 +13198,13 @@
         </is>
       </c>
       <c r="AA57" s="3">
-        <v>53.05979156494141</v>
+        <v>53.05979</v>
       </c>
       <c r="AB57" s="3">
-        <v>35.42341613769531</v>
+        <v>35.423416</v>
       </c>
       <c r="AC57" s="3">
-        <v>51.72472381591797</v>
+        <v>51.724724</v>
       </c>
       <c r="AD57" s="3">
         <v>0</v>
@@ -13216,55 +13216,55 @@
         <v>0</v>
       </c>
       <c r="AG57" s="3">
-        <v>0.1393988430500031</v>
+        <v>0.13939884</v>
       </c>
       <c r="AH57" s="3">
-        <v>0.1986805945634842</v>
+        <v>0.1986806</v>
       </c>
       <c r="AI57" s="3">
-        <v>0.9021158218383789</v>
+        <v>0.9021158</v>
       </c>
       <c r="AJ57" s="3">
-        <v>0.1073329076170921</v>
+        <v>0.10733291</v>
       </c>
       <c r="AK57" s="3">
-        <v>0.7084113359451294</v>
+        <v>0.7084113399999999</v>
       </c>
       <c r="AL57" s="3">
-        <v>0.2208583652973175</v>
+        <v>0.22085837</v>
       </c>
       <c r="AM57" s="3">
-        <v>0.5995329618453979</v>
+        <v>0.59953296</v>
       </c>
       <c r="AN57" s="3">
-        <v>0.7913217544555664</v>
+        <v>0.79132175</v>
       </c>
       <c r="AO57" s="3">
-        <v>0.08487884700298309</v>
+        <v>0.08487885000000001</v>
       </c>
       <c r="AP57" s="3">
-        <v>0.9457699060440063</v>
+        <v>0.9457699000000001</v>
       </c>
       <c r="AQ57" s="3">
-        <v>0.9987918138504028</v>
+        <v>0.9987918</v>
       </c>
       <c r="AR57" s="3">
-        <v>0.7637178301811218</v>
+        <v>0.76371783</v>
       </c>
       <c r="AS57" s="3">
-        <v>0.9264180064201355</v>
+        <v>0.926418</v>
       </c>
       <c r="AT57" s="3">
-        <v>0.7933618426322937</v>
+        <v>0.79336184</v>
       </c>
       <c r="AU57" s="3">
-        <v>-4.793391704559326</v>
+        <v>-4.7933917</v>
       </c>
       <c r="AV57" s="3">
-        <v>103.0428466796875</v>
+        <v>103.04285</v>
       </c>
       <c r="AW57" s="3">
-        <v>5.665875434875488</v>
+        <v>5.6658754</v>
       </c>
       <c r="AX57" s="3">
         <v>416.5290000000002</v>
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="AA58" s="3">
-        <v>57.47060394287109</v>
+        <v>57.470604</v>
       </c>
       <c r="AB58" s="3">
-        <v>52.83766937255859</v>
+        <v>52.83767</v>
       </c>
       <c r="AC58" s="3">
-        <v>40.26141738891602</v>
+        <v>40.261417</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -13397,55 +13397,55 @@
         <v>0</v>
       </c>
       <c r="AG58" s="3">
-        <v>0.1706415861845016</v>
+        <v>0.17064159</v>
       </c>
       <c r="AH58" s="3">
-        <v>0.1931375116109848</v>
+        <v>0.19313751</v>
       </c>
       <c r="AI58" s="3">
-        <v>0.8912813067436218</v>
+        <v>0.8912813000000001</v>
       </c>
       <c r="AJ58" s="3">
-        <v>0.07847318053245544</v>
+        <v>0.07847318</v>
       </c>
       <c r="AK58" s="3">
-        <v>0.7500410079956055</v>
+        <v>0.750041</v>
       </c>
       <c r="AL58" s="3">
-        <v>0.294198751449585</v>
+        <v>0.29419875</v>
       </c>
       <c r="AM58" s="3">
-        <v>0.7222768068313599</v>
+        <v>0.7222768000000001</v>
       </c>
       <c r="AN58" s="3">
-        <v>0.8761817812919617</v>
+        <v>0.8761818</v>
       </c>
       <c r="AO58" s="3">
-        <v>0.1026869863271713</v>
+        <v>0.10268699</v>
       </c>
       <c r="AP58" s="3">
-        <v>0.9765962362289429</v>
+        <v>0.97659624</v>
       </c>
       <c r="AQ58" s="3">
-        <v>0.9998048543930054</v>
+        <v>0.99980485</v>
       </c>
       <c r="AR58" s="3">
-        <v>0.7163273096084595</v>
+        <v>0.7163273</v>
       </c>
       <c r="AS58" s="3">
-        <v>0.9506087303161621</v>
+        <v>0.95060873</v>
       </c>
       <c r="AT58" s="3">
-        <v>0.8373674154281616</v>
+        <v>0.8373674</v>
       </c>
       <c r="AU58" s="3">
-        <v>-4.716939926147461</v>
+        <v>-4.71694</v>
       </c>
       <c r="AV58" s="3">
-        <v>102.2067489624023</v>
+        <v>102.20675</v>
       </c>
       <c r="AW58" s="3">
-        <v>5.249889373779297</v>
+        <v>5.2498894</v>
       </c>
       <c r="AX58" s="3">
         <v>416.5290000000002</v>
@@ -13560,13 +13560,13 @@
         </is>
       </c>
       <c r="AA59" s="3">
-        <v>53.13330078125</v>
+        <v>53.1333</v>
       </c>
       <c r="AB59" s="3">
-        <v>44.24358749389648</v>
+        <v>44.243587</v>
       </c>
       <c r="AC59" s="3">
-        <v>42.96165084838867</v>
+        <v>42.96165</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
@@ -13578,55 +13578,55 @@
         <v>0</v>
       </c>
       <c r="AG59" s="3">
-        <v>0.190639853477478</v>
+        <v>0.19063985</v>
       </c>
       <c r="AH59" s="3">
-        <v>0.2949622273445129</v>
+        <v>0.29496223</v>
       </c>
       <c r="AI59" s="3">
-        <v>0.8241535425186157</v>
+        <v>0.82415354</v>
       </c>
       <c r="AJ59" s="3">
-        <v>0.08000024408102036</v>
+        <v>0.080000244</v>
       </c>
       <c r="AK59" s="3">
-        <v>0.8343261480331421</v>
+        <v>0.83432615</v>
       </c>
       <c r="AL59" s="3">
-        <v>0.07658106088638306</v>
+        <v>0.07658106000000001</v>
       </c>
       <c r="AM59" s="3">
-        <v>0.5124601125717163</v>
+        <v>0.5124601</v>
       </c>
       <c r="AN59" s="3">
-        <v>0.6167970299720764</v>
+        <v>0.61679703</v>
       </c>
       <c r="AO59" s="3">
-        <v>0.094986192882061</v>
+        <v>0.09498619</v>
       </c>
       <c r="AP59" s="3">
-        <v>0.9500174522399902</v>
+        <v>0.95001745</v>
       </c>
       <c r="AQ59" s="3">
-        <v>0.9997907876968384</v>
+        <v>0.9997908</v>
       </c>
       <c r="AR59" s="3">
-        <v>0.7742282748222351</v>
+        <v>0.7742283</v>
       </c>
       <c r="AS59" s="3">
-        <v>0.949169933795929</v>
+        <v>0.9491699300000001</v>
       </c>
       <c r="AT59" s="3">
-        <v>0.8440155982971191</v>
+        <v>0.8440156</v>
       </c>
       <c r="AU59" s="3">
-        <v>-4.929348468780518</v>
+        <v>-4.9293485</v>
       </c>
       <c r="AV59" s="3">
-        <v>98.57073974609375</v>
+        <v>98.57074</v>
       </c>
       <c r="AW59" s="3">
-        <v>11.26975059509277</v>
+        <v>11.269751</v>
       </c>
       <c r="AX59" s="3">
         <v>435.5720000000002</v>
@@ -13741,13 +13741,13 @@
         </is>
       </c>
       <c r="AA60" s="3">
-        <v>64.6365966796875</v>
+        <v>64.6366</v>
       </c>
       <c r="AB60" s="3">
-        <v>44.51011276245117</v>
+        <v>44.510113</v>
       </c>
       <c r="AC60" s="3">
-        <v>43.77297210693359</v>
+        <v>43.772972</v>
       </c>
       <c r="AD60" s="3">
         <v>0</v>
@@ -13759,55 +13759,55 @@
         <v>0</v>
       </c>
       <c r="AG60" s="3">
-        <v>0.07870471477508545</v>
+        <v>0.07870471499999999</v>
       </c>
       <c r="AH60" s="3">
-        <v>0.4484577775001526</v>
+        <v>0.44845778</v>
       </c>
       <c r="AI60" s="3">
-        <v>0.8194307088851929</v>
+        <v>0.8194307</v>
       </c>
       <c r="AJ60" s="3">
-        <v>0.08472548425197601</v>
+        <v>0.084725484</v>
       </c>
       <c r="AK60" s="3">
-        <v>0.9327059984207153</v>
+        <v>0.932706</v>
       </c>
       <c r="AL60" s="3">
-        <v>0.1746114790439606</v>
+        <v>0.17461148</v>
       </c>
       <c r="AM60" s="3">
-        <v>0.6978225708007812</v>
+        <v>0.6978226</v>
       </c>
       <c r="AN60" s="3">
-        <v>0.8456341624259949</v>
+        <v>0.84563416</v>
       </c>
       <c r="AO60" s="3">
-        <v>0.2804053723812103</v>
+        <v>0.28040537</v>
       </c>
       <c r="AP60" s="3">
-        <v>0.9811990857124329</v>
+        <v>0.9811991</v>
       </c>
       <c r="AQ60" s="3">
-        <v>0.9999188184738159</v>
+        <v>0.9999188</v>
       </c>
       <c r="AR60" s="3">
-        <v>0.7408477067947388</v>
+        <v>0.7408477</v>
       </c>
       <c r="AS60" s="3">
-        <v>0.944384753704071</v>
+        <v>0.94438475</v>
       </c>
       <c r="AT60" s="3">
-        <v>0.8860940933227539</v>
+        <v>0.8860941</v>
       </c>
       <c r="AU60" s="3">
-        <v>-4.941195487976074</v>
+        <v>-4.9411955</v>
       </c>
       <c r="AV60" s="3">
-        <v>100.9640350341797</v>
+        <v>100.964035</v>
       </c>
       <c r="AW60" s="3">
-        <v>8.008500099182129</v>
+        <v>8.0085</v>
       </c>
       <c r="AX60" s="3">
         <v>458.6100000000002</v>
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="AA61" s="3">
-        <v>42.54349136352539</v>
+        <v>42.54349</v>
       </c>
       <c r="AB61" s="3">
-        <v>23.04730606079102</v>
+        <v>23.047306</v>
       </c>
       <c r="AC61" s="3">
-        <v>45.96738433837891</v>
+        <v>45.967384</v>
       </c>
       <c r="AD61" s="3">
         <v>0</v>
@@ -13940,55 +13940,55 @@
         <v>0</v>
       </c>
       <c r="AG61" s="3">
-        <v>0.06970883905887604</v>
+        <v>0.06970883999999999</v>
       </c>
       <c r="AH61" s="3">
-        <v>0.2512701451778412</v>
+        <v>0.25127015</v>
       </c>
       <c r="AI61" s="3">
-        <v>0.8532727956771851</v>
+        <v>0.8532728000000001</v>
       </c>
       <c r="AJ61" s="3">
-        <v>0.1371862292289734</v>
+        <v>0.13718623</v>
       </c>
       <c r="AK61" s="3">
-        <v>0.7447241544723511</v>
+        <v>0.74472415</v>
       </c>
       <c r="AL61" s="3">
-        <v>0.03474078327417374</v>
+        <v>0.034740783</v>
       </c>
       <c r="AM61" s="3">
-        <v>0.2177871912717819</v>
+        <v>0.21778719</v>
       </c>
       <c r="AN61" s="3">
-        <v>0.577147364616394</v>
+        <v>0.57714736</v>
       </c>
       <c r="AO61" s="3">
-        <v>0.1105703935027122</v>
+        <v>0.11057039</v>
       </c>
       <c r="AP61" s="3">
-        <v>0.9659855961799622</v>
+        <v>0.9659856</v>
       </c>
       <c r="AQ61" s="3">
-        <v>0.9978991746902466</v>
+        <v>0.9978992</v>
       </c>
       <c r="AR61" s="3">
-        <v>0.8094357252120972</v>
+        <v>0.8094357</v>
       </c>
       <c r="AS61" s="3">
-        <v>0.8139773607254028</v>
+        <v>0.81397736</v>
       </c>
       <c r="AT61" s="3">
-        <v>0.805046558380127</v>
+        <v>0.80504656</v>
       </c>
       <c r="AU61" s="3">
-        <v>-5.245954036712646</v>
+        <v>-5.245954</v>
       </c>
       <c r="AV61" s="3">
-        <v>95.96076965332031</v>
+        <v>95.96077</v>
       </c>
       <c r="AW61" s="3">
-        <v>7.14786434173584</v>
+        <v>7.1478643</v>
       </c>
       <c r="AX61" s="3">
         <v>494.6610000000003</v>
@@ -14103,13 +14103,13 @@
         </is>
       </c>
       <c r="AA62" s="3">
-        <v>44.82749176025391</v>
+        <v>44.82749</v>
       </c>
       <c r="AB62" s="3">
-        <v>33.07476043701172</v>
+        <v>33.07476</v>
       </c>
       <c r="AC62" s="3">
-        <v>47.28740692138672</v>
+        <v>47.287407</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -14121,55 +14121,55 @@
         <v>0</v>
       </c>
       <c r="AG62" s="3">
-        <v>0.1210609823465347</v>
+        <v>0.12106098</v>
       </c>
       <c r="AH62" s="3">
-        <v>0.57117760181427</v>
+        <v>0.5711776</v>
       </c>
       <c r="AI62" s="3">
-        <v>0.7225996851921082</v>
+        <v>0.7225997</v>
       </c>
       <c r="AJ62" s="3">
-        <v>0.1377389132976532</v>
+        <v>0.13773891</v>
       </c>
       <c r="AK62" s="3">
-        <v>0.9282013177871704</v>
+        <v>0.9282013</v>
       </c>
       <c r="AL62" s="3">
-        <v>0.2312162667512894</v>
+        <v>0.23121627</v>
       </c>
       <c r="AM62" s="3">
-        <v>0.3574883341789246</v>
+        <v>0.35748833</v>
       </c>
       <c r="AN62" s="3">
-        <v>0.5374731421470642</v>
+        <v>0.53747314</v>
       </c>
       <c r="AO62" s="3">
-        <v>0.2994638681411743</v>
+        <v>0.29946387</v>
       </c>
       <c r="AP62" s="3">
-        <v>0.9403905868530273</v>
+        <v>0.9403906</v>
       </c>
       <c r="AQ62" s="3">
-        <v>0.9997075796127319</v>
+        <v>0.9997076</v>
       </c>
       <c r="AR62" s="3">
-        <v>0.8253836631774902</v>
+        <v>0.82538366</v>
       </c>
       <c r="AS62" s="3">
-        <v>0.9273607134819031</v>
+        <v>0.9273607</v>
       </c>
       <c r="AT62" s="3">
-        <v>0.7729440331459045</v>
+        <v>0.77294403</v>
       </c>
       <c r="AU62" s="3">
-        <v>-5.20426082611084</v>
+        <v>-5.204261</v>
       </c>
       <c r="AV62" s="3">
-        <v>97.1646728515625</v>
+        <v>97.16467</v>
       </c>
       <c r="AW62" s="3">
-        <v>13.03351020812988</v>
+        <v>13.03351</v>
       </c>
       <c r="AX62" s="3">
         <v>448.6150000000002</v>
@@ -14261,7 +14261,7 @@
         <v>239.5164586901131</v>
       </c>
       <c r="T63" s="3">
-        <v>3.620664638104531</v>
+        <v>3.62066463810453</v>
       </c>
       <c r="U63" s="3">
         <v>5.889959235273289</v>
@@ -14273,7 +14273,7 @@
         <v>3.478100000000002</v>
       </c>
       <c r="X63" s="3">
-        <v>-5.661180148460343</v>
+        <v>-5.661180148460344</v>
       </c>
       <c r="Y63" s="3">
         <v>2.181824687608449E-06</v>
@@ -14284,13 +14284,13 @@
         </is>
       </c>
       <c r="AA63" s="3">
-        <v>41.35836791992188</v>
+        <v>41.358368</v>
       </c>
       <c r="AB63" s="3">
-        <v>33.96128845214844</v>
+        <v>33.96129</v>
       </c>
       <c r="AC63" s="3">
-        <v>42.29502868652344</v>
+        <v>42.29503</v>
       </c>
       <c r="AD63" s="3">
         <v>0</v>
@@ -14302,55 +14302,55 @@
         <v>0</v>
       </c>
       <c r="AG63" s="3">
-        <v>0.09930116683244705</v>
+        <v>0.09930116999999999</v>
       </c>
       <c r="AH63" s="3">
-        <v>0.3533108234405518</v>
+        <v>0.35331082</v>
       </c>
       <c r="AI63" s="3">
-        <v>0.8536133766174316</v>
+        <v>0.8536134</v>
       </c>
       <c r="AJ63" s="3">
-        <v>0.1031600460410118</v>
+        <v>0.103160046</v>
       </c>
       <c r="AK63" s="3">
-        <v>0.8321025967597961</v>
+        <v>0.8321026</v>
       </c>
       <c r="AL63" s="3">
-        <v>0.07893901318311691</v>
+        <v>0.07893901</v>
       </c>
       <c r="AM63" s="3">
-        <v>0.4102925658226013</v>
+        <v>0.41029257</v>
       </c>
       <c r="AN63" s="3">
-        <v>0.7070093750953674</v>
+        <v>0.7070094</v>
       </c>
       <c r="AO63" s="3">
-        <v>0.1405244171619415</v>
+        <v>0.14052442</v>
       </c>
       <c r="AP63" s="3">
-        <v>0.9609413146972656</v>
+        <v>0.9609413</v>
       </c>
       <c r="AQ63" s="3">
-        <v>0.9991549253463745</v>
+        <v>0.9991549</v>
       </c>
       <c r="AR63" s="3">
-        <v>0.7503408193588257</v>
+        <v>0.7503408</v>
       </c>
       <c r="AS63" s="3">
-        <v>0.8815935254096985</v>
+        <v>0.8815935</v>
       </c>
       <c r="AT63" s="3">
-        <v>0.8954097628593445</v>
+        <v>0.8954097600000001</v>
       </c>
       <c r="AU63" s="3">
-        <v>-5.118796348571777</v>
+        <v>-5.1187963</v>
       </c>
       <c r="AV63" s="3">
-        <v>97.54644775390625</v>
+        <v>97.54644999999999</v>
       </c>
       <c r="AW63" s="3">
-        <v>9.896895408630371</v>
+        <v>9.896895000000001</v>
       </c>
       <c r="AX63" s="3">
         <v>488.6320000000003</v>
@@ -14465,13 +14465,13 @@
         </is>
       </c>
       <c r="AA64" s="3">
-        <v>37.92741394042969</v>
+        <v>37.927414</v>
       </c>
       <c r="AB64" s="3">
-        <v>30.6676139831543</v>
+        <v>30.667614</v>
       </c>
       <c r="AC64" s="3">
-        <v>43.71705627441406</v>
+        <v>43.717056</v>
       </c>
       <c r="AD64" s="3">
         <v>0</v>
@@ -14483,55 +14483,55 @@
         <v>0</v>
       </c>
       <c r="AG64" s="3">
-        <v>0.09371493756771088</v>
+        <v>0.09371494</v>
       </c>
       <c r="AH64" s="3">
-        <v>0.3201565742492676</v>
+        <v>0.32015657</v>
       </c>
       <c r="AI64" s="3">
-        <v>0.8501707315444946</v>
+        <v>0.85017073</v>
       </c>
       <c r="AJ64" s="3">
-        <v>0.1019221693277359</v>
+        <v>0.10192217</v>
       </c>
       <c r="AK64" s="3">
-        <v>0.7625911235809326</v>
+        <v>0.7625911</v>
       </c>
       <c r="AL64" s="3">
-        <v>0.03210257738828659</v>
+        <v>0.032102577</v>
       </c>
       <c r="AM64" s="3">
-        <v>0.2855415344238281</v>
+        <v>0.28554153</v>
       </c>
       <c r="AN64" s="3">
-        <v>0.5882561802864075</v>
+        <v>0.5882562</v>
       </c>
       <c r="AO64" s="3">
-        <v>0.100622296333313</v>
+        <v>0.1006223</v>
       </c>
       <c r="AP64" s="3">
-        <v>0.9183708429336548</v>
+        <v>0.91837084</v>
       </c>
       <c r="AQ64" s="3">
-        <v>0.997296929359436</v>
+        <v>0.9972969</v>
       </c>
       <c r="AR64" s="3">
-        <v>0.7594398260116577</v>
+        <v>0.7594398</v>
       </c>
       <c r="AS64" s="3">
-        <v>0.805336594581604</v>
+        <v>0.8053366</v>
       </c>
       <c r="AT64" s="3">
-        <v>0.8535860776901245</v>
+        <v>0.8535861</v>
       </c>
       <c r="AU64" s="3">
-        <v>-5.144351959228516</v>
+        <v>-5.144352</v>
       </c>
       <c r="AV64" s="3">
-        <v>96.48191833496094</v>
+        <v>96.48192</v>
       </c>
       <c r="AW64" s="3">
-        <v>10.30197334289551</v>
+        <v>10.301973</v>
       </c>
       <c r="AX64" s="3">
         <v>488.6320000000003</v>
@@ -14646,13 +14646,13 @@
         </is>
       </c>
       <c r="AA65" s="3">
-        <v>41.94546508789062</v>
+        <v>41.945465</v>
       </c>
       <c r="AB65" s="3">
-        <v>33.05574798583984</v>
+        <v>33.055748</v>
       </c>
       <c r="AC65" s="3">
-        <v>43.53328323364258</v>
+        <v>43.533283</v>
       </c>
       <c r="AD65" s="3">
         <v>0</v>
@@ -14664,55 +14664,55 @@
         <v>0</v>
       </c>
       <c r="AG65" s="3">
-        <v>0.06773050129413605</v>
+        <v>0.0677305</v>
       </c>
       <c r="AH65" s="3">
-        <v>0.5890909433364868</v>
+        <v>0.58909094</v>
       </c>
       <c r="AI65" s="3">
-        <v>0.8289631605148315</v>
+        <v>0.82896316</v>
       </c>
       <c r="AJ65" s="3">
-        <v>0.1782760918140411</v>
+        <v>0.17827609</v>
       </c>
       <c r="AK65" s="3">
-        <v>0.9205002784729004</v>
+        <v>0.9205003</v>
       </c>
       <c r="AL65" s="3">
-        <v>0.4137061238288879</v>
+        <v>0.41370612</v>
       </c>
       <c r="AM65" s="3">
-        <v>0.4533693790435791</v>
+        <v>0.45336938</v>
       </c>
       <c r="AN65" s="3">
-        <v>0.6987740993499756</v>
+        <v>0.6987741</v>
       </c>
       <c r="AO65" s="3">
-        <v>0.2673107385635376</v>
+        <v>0.26731074</v>
       </c>
       <c r="AP65" s="3">
-        <v>0.9421643018722534</v>
+        <v>0.9421643</v>
       </c>
       <c r="AQ65" s="3">
-        <v>0.9997745752334595</v>
+        <v>0.9997746</v>
       </c>
       <c r="AR65" s="3">
-        <v>0.8696621060371399</v>
+        <v>0.8696621</v>
       </c>
       <c r="AS65" s="3">
-        <v>0.9257358312606812</v>
+        <v>0.92573583</v>
       </c>
       <c r="AT65" s="3">
-        <v>0.7252635955810547</v>
+        <v>0.7252636</v>
       </c>
       <c r="AU65" s="3">
-        <v>-5.300406455993652</v>
+        <v>-5.3004065</v>
       </c>
       <c r="AV65" s="3">
-        <v>95.94831848144531</v>
+        <v>95.94832</v>
       </c>
       <c r="AW65" s="3">
-        <v>12.00407409667969</v>
+        <v>12.004074</v>
       </c>
       <c r="AX65" s="3">
         <v>446.5990000000002</v>
